--- a/research/traditional_assets/database/data/new_zealand/new_zealand_diversified.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07733139435579917</v>
+        <v>0.07714726645160293</v>
       </c>
       <c r="C2">
-        <v>9221.951741687113</v>
+        <v>9166.066202309217</v>
       </c>
       <c r="D2">
-        <v>8906.051741687113</v>
+        <v>8958.364202309218</v>
       </c>
       <c r="E2">
-        <v>-3988.2</v>
+        <v>-3880.002</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>108.198</v>
       </c>
       <c r="G2">
         <v>315.9</v>
@@ -1445,28 +1445,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.442359399999999</v>
       </c>
       <c r="N2">
-        <v>361.4666666666668</v>
+        <v>356.0243072666668</v>
       </c>
       <c r="O2">
-        <v>101.2106666666667</v>
+        <v>99.6868060346667</v>
       </c>
       <c r="P2">
-        <v>260.2560000000001</v>
+        <v>256.3375012320001</v>
       </c>
       <c r="Q2">
-        <v>705.4560000000001</v>
+        <v>701.5375012320001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07733139435579917</v>
+        <v>0.07756071358747771</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7335037780017946</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.41727238128868</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07714726645160293</v>
+        <v>0.07696313854740669</v>
       </c>
       <c r="C3">
-        <v>9166.066202309217</v>
+        <v>9110.798840957457</v>
       </c>
       <c r="D3">
-        <v>8958.364202309218</v>
+        <v>9011.294840957458</v>
       </c>
       <c r="E3">
-        <v>-3880.002</v>
+        <v>-3771.804</v>
       </c>
       <c r="F3">
-        <v>108.198</v>
+        <v>216.396</v>
       </c>
       <c r="G3">
         <v>315.9</v>
@@ -1527,28 +1527,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M3">
-        <v>5.442359399999999</v>
+        <v>10.8847188</v>
       </c>
       <c r="N3">
-        <v>356.0243072666668</v>
+        <v>350.5819478666668</v>
       </c>
       <c r="O3">
-        <v>99.6868060346667</v>
+        <v>98.16294540266671</v>
       </c>
       <c r="P3">
-        <v>256.3375012320001</v>
+        <v>252.4190024640001</v>
       </c>
       <c r="Q3">
-        <v>701.5375012320001</v>
+        <v>697.619002464</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07756071358747771</v>
+        <v>0.07779471280347622</v>
       </c>
       <c r="T3">
-        <v>0.7335037780017946</v>
+        <v>0.7389079169394044</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.41727238128868</v>
+        <v>33.20863619064434</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07696313854740669</v>
+        <v>0.07677901064321045</v>
       </c>
       <c r="C4">
-        <v>9110.798840957457</v>
+        <v>9056.160680303828</v>
       </c>
       <c r="D4">
-        <v>9011.294840957458</v>
+        <v>9064.854680303828</v>
       </c>
       <c r="E4">
-        <v>-3771.804</v>
+        <v>-3663.606</v>
       </c>
       <c r="F4">
-        <v>216.396</v>
+        <v>324.594</v>
       </c>
       <c r="G4">
         <v>315.9</v>
@@ -1609,28 +1609,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M4">
-        <v>10.8847188</v>
+        <v>16.3270782</v>
       </c>
       <c r="N4">
-        <v>350.5819478666668</v>
+        <v>345.1395884666667</v>
       </c>
       <c r="O4">
-        <v>98.16294540266671</v>
+        <v>96.6390847706667</v>
       </c>
       <c r="P4">
-        <v>252.4190024640001</v>
+        <v>248.500503696</v>
       </c>
       <c r="Q4">
-        <v>697.619002464</v>
+        <v>693.7005036960001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07779471280347622</v>
+        <v>0.07803353674557778</v>
       </c>
       <c r="T4">
-        <v>0.7389079169394044</v>
+        <v>0.7444234814221198</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.20863619064434</v>
+        <v>22.13909079376289</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07677901064321045</v>
+        <v>0.07659488273901421</v>
       </c>
       <c r="C5">
-        <v>9056.160680303828</v>
+        <v>9002.163006646142</v>
       </c>
       <c r="D5">
-        <v>9064.854680303828</v>
+        <v>9119.055006646142</v>
       </c>
       <c r="E5">
-        <v>-3663.606</v>
+        <v>-3555.408</v>
       </c>
       <c r="F5">
-        <v>324.594</v>
+        <v>432.792</v>
       </c>
       <c r="G5">
         <v>315.9</v>
@@ -1691,28 +1691,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M5">
-        <v>16.3270782</v>
+        <v>21.7694376</v>
       </c>
       <c r="N5">
-        <v>345.1395884666667</v>
+        <v>339.6972290666668</v>
       </c>
       <c r="O5">
-        <v>96.6390847706667</v>
+        <v>95.1152241386667</v>
       </c>
       <c r="P5">
-        <v>248.500503696</v>
+        <v>244.5820049280001</v>
       </c>
       <c r="Q5">
-        <v>693.7005036960001</v>
+        <v>689.7820049280001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07803353674557778</v>
+        <v>0.07827733618647315</v>
       </c>
       <c r="T5">
-        <v>0.7444234814221198</v>
+        <v>0.7500539534982249</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.13909079376289</v>
+        <v>16.60431809532217</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07659488273901421</v>
+        <v>0.07641075483481798</v>
       </c>
       <c r="C6">
-        <v>9002.163006646142</v>
+        <v>8948.817377836744</v>
       </c>
       <c r="D6">
-        <v>9119.055006646142</v>
+        <v>9173.907377836744</v>
       </c>
       <c r="E6">
-        <v>-3555.408</v>
+        <v>-3447.21</v>
       </c>
       <c r="F6">
-        <v>432.792</v>
+        <v>540.99</v>
       </c>
       <c r="G6">
         <v>315.9</v>
@@ -1773,28 +1773,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M6">
-        <v>21.7694376</v>
+        <v>27.211797</v>
       </c>
       <c r="N6">
-        <v>339.6972290666668</v>
+        <v>334.2548696666668</v>
       </c>
       <c r="O6">
-        <v>95.1152241386667</v>
+        <v>93.59136350666671</v>
       </c>
       <c r="P6">
-        <v>244.5820049280001</v>
+        <v>240.6635061600001</v>
       </c>
       <c r="Q6">
-        <v>689.7820049280001</v>
+        <v>685.86350616</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07827733618647315</v>
+        <v>0.07852626824717682</v>
       </c>
       <c r="T6">
-        <v>0.7500539534982249</v>
+        <v>0.7558029618285639</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.60431809532217</v>
+        <v>13.28345447625773</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07641075483481798</v>
+        <v>0.07622662693062172</v>
       </c>
       <c r="C7">
-        <v>8948.817377836744</v>
+        <v>8896.135631499143</v>
       </c>
       <c r="D7">
-        <v>9173.907377836744</v>
+        <v>9229.423631499143</v>
       </c>
       <c r="E7">
-        <v>-3447.21</v>
+        <v>-3339.012</v>
       </c>
       <c r="F7">
-        <v>540.99</v>
+        <v>649.188</v>
       </c>
       <c r="G7">
         <v>315.9</v>
@@ -1855,28 +1855,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M7">
-        <v>27.211797</v>
+        <v>32.6541564</v>
       </c>
       <c r="N7">
-        <v>334.2548696666668</v>
+        <v>328.8125102666668</v>
       </c>
       <c r="O7">
-        <v>93.59136350666671</v>
+        <v>92.0675028746667</v>
       </c>
       <c r="P7">
-        <v>240.6635061600001</v>
+        <v>236.7450073920001</v>
       </c>
       <c r="Q7">
-        <v>685.86350616</v>
+        <v>681.9450073920001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07852626824717682</v>
+        <v>0.07878049673470397</v>
       </c>
       <c r="T7">
-        <v>0.7558029618285639</v>
+        <v>0.7616742894850803</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.28345447625773</v>
+        <v>11.06954539688144</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07622662693062172</v>
+        <v>0.0760424990264255</v>
       </c>
       <c r="C8">
-        <v>8896.135631499143</v>
+        <v>8844.129893544754</v>
       </c>
       <c r="D8">
-        <v>9229.423631499143</v>
+        <v>9285.615893544755</v>
       </c>
       <c r="E8">
-        <v>-3339.012</v>
+        <v>-3230.814</v>
       </c>
       <c r="F8">
-        <v>649.188</v>
+        <v>757.3859999999999</v>
       </c>
       <c r="G8">
         <v>315.9</v>
@@ -1937,28 +1937,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M8">
-        <v>32.6541564</v>
+        <v>38.09651579999999</v>
       </c>
       <c r="N8">
-        <v>328.8125102666668</v>
+        <v>323.3701508666668</v>
       </c>
       <c r="O8">
-        <v>92.0675028746667</v>
+        <v>90.54364224266671</v>
       </c>
       <c r="P8">
-        <v>236.7450073920001</v>
+        <v>232.8265086240001</v>
       </c>
       <c r="Q8">
-        <v>681.9450073920001</v>
+        <v>678.0265086240001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07878049673470397</v>
+        <v>0.0790401925015328</v>
       </c>
       <c r="T8">
-        <v>0.7616742894850803</v>
+        <v>0.7676718822524895</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.06954539688144</v>
+        <v>9.488181768755526</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0760424990264255</v>
+        <v>0.07594477112222926</v>
       </c>
       <c r="C9">
-        <v>8844.129893544754</v>
+        <v>8766.035415537603</v>
       </c>
       <c r="D9">
-        <v>9285.615893544755</v>
+        <v>9315.719415537604</v>
       </c>
       <c r="E9">
-        <v>-3230.814</v>
+        <v>-3122.616</v>
       </c>
       <c r="F9">
-        <v>757.386</v>
+        <v>865.5839999999999</v>
       </c>
       <c r="G9">
         <v>315.9</v>
@@ -2019,45 +2019,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M9">
-        <v>38.0965158</v>
+        <v>44.8372512</v>
       </c>
       <c r="N9">
-        <v>323.3701508666667</v>
+        <v>316.6294154666667</v>
       </c>
       <c r="O9">
-        <v>90.54364224266669</v>
+        <v>88.65623633066669</v>
       </c>
       <c r="P9">
-        <v>232.826508624</v>
+        <v>227.9731791360001</v>
       </c>
       <c r="Q9">
-        <v>678.026508624</v>
+        <v>673.173179136</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0790401925015328</v>
+        <v>0.07930553382851006</v>
       </c>
       <c r="T9">
-        <v>0.7676718822524895</v>
+        <v>0.7737998574713641</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.28</v>
       </c>
       <c r="W9">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.488181768755524</v>
+        <v>8.061749036628427</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07594477112222926</v>
+        <v>0.07577144321803303</v>
       </c>
       <c r="C10">
-        <v>8766.035415537603</v>
+        <v>8711.711168317175</v>
       </c>
       <c r="D10">
-        <v>9315.719415537604</v>
+        <v>9369.593168317175</v>
       </c>
       <c r="E10">
-        <v>-3122.616</v>
+        <v>-3014.418</v>
       </c>
       <c r="F10">
-        <v>865.5839999999999</v>
+        <v>973.7819999999999</v>
       </c>
       <c r="G10">
         <v>315.9</v>
@@ -2101,28 +2101,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M10">
-        <v>44.8372512</v>
+        <v>50.44190759999999</v>
       </c>
       <c r="N10">
-        <v>316.6294154666667</v>
+        <v>311.0247590666668</v>
       </c>
       <c r="O10">
-        <v>88.65623633066669</v>
+        <v>87.0869325386667</v>
       </c>
       <c r="P10">
-        <v>227.9731791360001</v>
+        <v>223.9378265280001</v>
       </c>
       <c r="Q10">
-        <v>673.173179136</v>
+        <v>669.137826528</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07930553382851006</v>
+        <v>0.07957670683300333</v>
       </c>
       <c r="T10">
-        <v>0.7737998574713641</v>
+        <v>0.7800625134642801</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.061749036628427</v>
+        <v>7.165999143669714</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07577144321803303</v>
+        <v>0.07572051531383678</v>
       </c>
       <c r="C11">
-        <v>8711.711168317175</v>
+        <v>8619.461213938341</v>
       </c>
       <c r="D11">
-        <v>9369.593168317175</v>
+        <v>9385.541213938341</v>
       </c>
       <c r="E11">
-        <v>-3014.418</v>
+        <v>-2906.22</v>
       </c>
       <c r="F11">
-        <v>973.7819999999999</v>
+        <v>1081.98</v>
       </c>
       <c r="G11">
         <v>315.9</v>
@@ -2183,45 +2183,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M11">
-        <v>50.44190759999999</v>
+        <v>57.88592999999999</v>
       </c>
       <c r="N11">
-        <v>311.0247590666668</v>
+        <v>303.5807366666668</v>
       </c>
       <c r="O11">
-        <v>87.0869325386667</v>
+        <v>85.0026062666667</v>
       </c>
       <c r="P11">
-        <v>223.9378265280001</v>
+        <v>218.5781304000001</v>
       </c>
       <c r="Q11">
-        <v>669.137826528</v>
+        <v>663.7781304</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07957670683300333</v>
+        <v>0.0798539059042631</v>
       </c>
       <c r="T11">
-        <v>0.7800625134642801</v>
+        <v>0.7864643395903718</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.165999143669714</v>
+        <v>6.244465048184711</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07572051531383678</v>
+        <v>0.07555942740964056</v>
       </c>
       <c r="C12">
-        <v>8619.461213938341</v>
+        <v>8562.067187519191</v>
       </c>
       <c r="D12">
-        <v>9385.541213938341</v>
+        <v>9436.345187519191</v>
       </c>
       <c r="E12">
-        <v>-2906.22</v>
+        <v>-2798.022</v>
       </c>
       <c r="F12">
-        <v>1081.98</v>
+        <v>1190.178</v>
       </c>
       <c r="G12">
         <v>315.9</v>
@@ -2265,28 +2265,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M12">
-        <v>57.88593</v>
+        <v>63.67452299999999</v>
       </c>
       <c r="N12">
-        <v>303.5807366666668</v>
+        <v>297.7921436666668</v>
       </c>
       <c r="O12">
-        <v>85.0026062666667</v>
+        <v>83.38180022666671</v>
       </c>
       <c r="P12">
-        <v>218.5781304000001</v>
+        <v>214.4103434400001</v>
       </c>
       <c r="Q12">
-        <v>663.7781304</v>
+        <v>659.6103434400001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0798539059042631</v>
+        <v>0.08013733416813545</v>
       </c>
       <c r="T12">
-        <v>0.7864643395903718</v>
+        <v>0.793010026977724</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.24446504818471</v>
+        <v>5.676786407440646</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07555942740964056</v>
+        <v>0.07546745950544431</v>
       </c>
       <c r="C13">
-        <v>8562.067187519191</v>
+        <v>8483.121469468348</v>
       </c>
       <c r="D13">
-        <v>9436.345187519191</v>
+        <v>9465.597469468348</v>
       </c>
       <c r="E13">
-        <v>-2798.022</v>
+        <v>-2689.824</v>
       </c>
       <c r="F13">
-        <v>1190.178</v>
+        <v>1298.376</v>
       </c>
       <c r="G13">
         <v>315.9</v>
@@ -2347,45 +2347,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M13">
-        <v>63.67452299999999</v>
+        <v>70.5018168</v>
       </c>
       <c r="N13">
-        <v>297.7921436666668</v>
+        <v>290.9648498666668</v>
       </c>
       <c r="O13">
-        <v>83.38180022666671</v>
+        <v>81.4701579626667</v>
       </c>
       <c r="P13">
-        <v>214.4103434400001</v>
+        <v>209.4946919040001</v>
       </c>
       <c r="Q13">
-        <v>659.6103434400001</v>
+        <v>654.6946919040001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08013733416813545</v>
+        <v>0.08042720398345944</v>
       </c>
       <c r="T13">
-        <v>0.793010026977724</v>
+        <v>0.799704479987516</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.676786407440646</v>
+        <v>5.127054635940485</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07546745950544431</v>
+        <v>0.07531213160124807</v>
       </c>
       <c r="C14">
-        <v>8483.121469468348</v>
+        <v>8424.742690823257</v>
       </c>
       <c r="D14">
-        <v>9465.597469468348</v>
+        <v>9515.416690823258</v>
       </c>
       <c r="E14">
-        <v>-2689.824</v>
+        <v>-2581.626</v>
       </c>
       <c r="F14">
-        <v>1298.376</v>
+        <v>1406.574</v>
       </c>
       <c r="G14">
         <v>315.9</v>
@@ -2429,28 +2429,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M14">
-        <v>70.5018168</v>
+        <v>76.37696819999999</v>
       </c>
       <c r="N14">
-        <v>290.9648498666668</v>
+        <v>285.0896984666667</v>
       </c>
       <c r="O14">
-        <v>81.4701579626667</v>
+        <v>79.8251155706667</v>
       </c>
       <c r="P14">
-        <v>209.4946919040001</v>
+        <v>205.264582896</v>
       </c>
       <c r="Q14">
-        <v>654.6946919040001</v>
+        <v>650.464582896</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08042720398345944</v>
+        <v>0.08072373747269893</v>
       </c>
       <c r="T14">
-        <v>0.799704479987516</v>
+        <v>0.8065528284687975</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.127054635940485</v>
+        <v>4.732665817791217</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07531213160124807</v>
+        <v>0.07515680369705183</v>
       </c>
       <c r="C15">
-        <v>8424.742690823257</v>
+        <v>8366.8911027621</v>
       </c>
       <c r="D15">
-        <v>9515.416690823258</v>
+        <v>9565.763102762101</v>
       </c>
       <c r="E15">
-        <v>-2581.626</v>
+        <v>-2473.428</v>
       </c>
       <c r="F15">
-        <v>1406.574</v>
+        <v>1514.772</v>
       </c>
       <c r="G15">
         <v>315.9</v>
@@ -2511,28 +2511,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M15">
-        <v>76.37696819999999</v>
+        <v>82.2521196</v>
       </c>
       <c r="N15">
-        <v>285.0896984666667</v>
+        <v>279.2145470666667</v>
       </c>
       <c r="O15">
-        <v>79.8251155706667</v>
+        <v>78.18007317866669</v>
       </c>
       <c r="P15">
-        <v>205.264582896</v>
+        <v>201.034473888</v>
       </c>
       <c r="Q15">
-        <v>650.464582896</v>
+        <v>646.234473888</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08072373747269893</v>
+        <v>0.08102716708959515</v>
       </c>
       <c r="T15">
-        <v>0.8065528284687975</v>
+        <v>0.8135604408682484</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.732665817791217</v>
+        <v>4.394618259377558</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07515680369705183</v>
+        <v>0.07510947579285561</v>
       </c>
       <c r="C16">
-        <v>8366.8911027621</v>
+        <v>8274.139558471199</v>
       </c>
       <c r="D16">
-        <v>9565.763102762101</v>
+        <v>9581.209558471199</v>
       </c>
       <c r="E16">
-        <v>-2473.428</v>
+        <v>-2365.23</v>
       </c>
       <c r="F16">
-        <v>1514.772</v>
+        <v>1622.97</v>
       </c>
       <c r="G16">
         <v>315.9</v>
@@ -2593,45 +2593,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M16">
-        <v>82.2521196</v>
+        <v>89.750241</v>
       </c>
       <c r="N16">
-        <v>279.2145470666667</v>
+        <v>271.7164256666667</v>
       </c>
       <c r="O16">
-        <v>78.18007317866669</v>
+        <v>76.08059918666669</v>
       </c>
       <c r="P16">
-        <v>201.034473888</v>
+        <v>195.63582648</v>
       </c>
       <c r="Q16">
-        <v>646.234473888</v>
+        <v>640.83582648</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08102716708959515</v>
+        <v>0.08133773622688895</v>
       </c>
       <c r="T16">
-        <v>0.8135604408682484</v>
+        <v>0.8207329382653334</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.394618259377558</v>
+        <v>4.027472936442217</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07510947579285561</v>
+        <v>0.07496134788865935</v>
       </c>
       <c r="C17">
-        <v>8274.139558471199</v>
+        <v>8214.610244739759</v>
       </c>
       <c r="D17">
-        <v>9581.209558471199</v>
+        <v>9629.878244739759</v>
       </c>
       <c r="E17">
-        <v>-2365.23</v>
+        <v>-2257.032</v>
       </c>
       <c r="F17">
-        <v>1622.97</v>
+        <v>1731.168</v>
       </c>
       <c r="G17">
         <v>315.9</v>
@@ -2675,28 +2675,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M17">
-        <v>89.75024099999999</v>
+        <v>95.7335904</v>
       </c>
       <c r="N17">
-        <v>271.7164256666667</v>
+        <v>265.7330762666668</v>
       </c>
       <c r="O17">
-        <v>76.08059918666669</v>
+        <v>74.40526135466671</v>
       </c>
       <c r="P17">
-        <v>195.63582648</v>
+        <v>191.3278149120001</v>
       </c>
       <c r="Q17">
-        <v>640.83582648</v>
+        <v>636.5278149120001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08133773622688895</v>
+        <v>0.08165569986745162</v>
       </c>
       <c r="T17">
-        <v>0.8207329382653334</v>
+        <v>0.8280762094099682</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.027472936442218</v>
+        <v>3.77575587791458</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07496134788865935</v>
+        <v>0.07481321998446314</v>
       </c>
       <c r="C18">
-        <v>8214.610244739759</v>
+        <v>8155.577890015324</v>
       </c>
       <c r="D18">
-        <v>9629.878244739759</v>
+        <v>9679.043890015324</v>
       </c>
       <c r="E18">
-        <v>-2257.032</v>
+        <v>-2148.834</v>
       </c>
       <c r="F18">
-        <v>1731.168</v>
+        <v>1839.366</v>
       </c>
       <c r="G18">
         <v>315.9</v>
@@ -2757,28 +2757,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M18">
-        <v>95.7335904</v>
+        <v>101.7169398</v>
       </c>
       <c r="N18">
-        <v>265.7330762666668</v>
+        <v>259.7497268666667</v>
       </c>
       <c r="O18">
-        <v>74.40526135466671</v>
+        <v>72.7299235226667</v>
       </c>
       <c r="P18">
-        <v>191.3278149120001</v>
+        <v>187.019803344</v>
       </c>
       <c r="Q18">
-        <v>636.5278149120001</v>
+        <v>632.219803344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08165569986745162</v>
+        <v>0.0819813252824857</v>
       </c>
       <c r="T18">
-        <v>0.8280762094099682</v>
+        <v>0.8355964268472446</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.77575587791458</v>
+        <v>3.553652590978427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07481321998446314</v>
+        <v>0.07466509208026688</v>
       </c>
       <c r="C19">
-        <v>8155.577890015324</v>
+        <v>8097.050145078591</v>
       </c>
       <c r="D19">
-        <v>9679.043890015324</v>
+        <v>9728.714145078591</v>
       </c>
       <c r="E19">
-        <v>-2148.834</v>
+        <v>-2040.636</v>
       </c>
       <c r="F19">
-        <v>1839.366</v>
+        <v>1947.564</v>
       </c>
       <c r="G19">
         <v>315.9</v>
@@ -2839,28 +2839,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M19">
-        <v>101.7169398</v>
+        <v>107.7002892</v>
       </c>
       <c r="N19">
-        <v>259.7497268666667</v>
+        <v>253.7663774666667</v>
       </c>
       <c r="O19">
-        <v>72.7299235226667</v>
+        <v>71.0545856906667</v>
       </c>
       <c r="P19">
-        <v>187.019803344</v>
+        <v>182.711791776</v>
       </c>
       <c r="Q19">
-        <v>632.219803344</v>
+        <v>627.911791776</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0819813252824857</v>
+        <v>0.08231489278081328</v>
       </c>
       <c r="T19">
-        <v>0.8355964268472446</v>
+        <v>0.8433000642220155</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.553652590978427</v>
+        <v>3.356227447035181</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07466509208026689</v>
+        <v>0.07451696417607065</v>
       </c>
       <c r="C20">
-        <v>8097.050145078585</v>
+        <v>8039.0348185673</v>
       </c>
       <c r="D20">
-        <v>9728.714145078586</v>
+        <v>9778.8968185673</v>
       </c>
       <c r="E20">
-        <v>-2040.636</v>
+        <v>-1932.438</v>
       </c>
       <c r="F20">
-        <v>1947.564</v>
+        <v>2055.762</v>
       </c>
       <c r="G20">
         <v>315.9</v>
@@ -2921,28 +2921,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M20">
-        <v>107.7002892</v>
+        <v>113.6836386</v>
       </c>
       <c r="N20">
-        <v>253.7663774666668</v>
+        <v>247.7830280666668</v>
       </c>
       <c r="O20">
-        <v>71.0545856906667</v>
+        <v>69.3792478586667</v>
       </c>
       <c r="P20">
-        <v>182.7117917760001</v>
+        <v>178.4037802080001</v>
       </c>
       <c r="Q20">
-        <v>627.9117917760001</v>
+        <v>623.603780208</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08231489278081328</v>
+        <v>0.08265669651366747</v>
       </c>
       <c r="T20">
-        <v>0.8433000642220155</v>
+        <v>0.8511939148652995</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.356227447035182</v>
+        <v>3.179583897191225</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07451696417607065</v>
+        <v>0.07436883627187442</v>
       </c>
       <c r="C21">
-        <v>8039.0348185673</v>
+        <v>7981.539881068716</v>
       </c>
       <c r="D21">
-        <v>9778.8968185673</v>
+        <v>9829.599881068716</v>
       </c>
       <c r="E21">
-        <v>-1932.438</v>
+        <v>-1824.24</v>
       </c>
       <c r="F21">
-        <v>2055.762</v>
+        <v>2163.96</v>
       </c>
       <c r="G21">
         <v>315.9</v>
@@ -3003,28 +3003,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M21">
-        <v>113.6836386</v>
+        <v>119.666988</v>
       </c>
       <c r="N21">
-        <v>247.7830280666668</v>
+        <v>241.7996786666668</v>
       </c>
       <c r="O21">
-        <v>69.3792478586667</v>
+        <v>67.70391002666669</v>
       </c>
       <c r="P21">
-        <v>178.4037802080001</v>
+        <v>174.0957686400001</v>
       </c>
       <c r="Q21">
-        <v>623.603780208</v>
+        <v>619.29576864</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08265669651366747</v>
+        <v>0.08300704533984302</v>
       </c>
       <c r="T21">
-        <v>0.8511939148652995</v>
+        <v>0.8592851117746654</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.179583897191225</v>
+        <v>3.020604702331664</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07436883627187442</v>
+        <v>0.07459870836767818</v>
       </c>
       <c r="C22">
-        <v>7981.539881068716</v>
+        <v>7794.881739845519</v>
       </c>
       <c r="D22">
-        <v>9829.599881068716</v>
+        <v>9751.139739845519</v>
       </c>
       <c r="E22">
-        <v>-1824.24</v>
+        <v>-1716.042</v>
       </c>
       <c r="F22">
-        <v>2163.96</v>
+        <v>2272.158</v>
       </c>
       <c r="G22">
         <v>315.9</v>
@@ -3085,45 +3085,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M22">
-        <v>119.666988</v>
+        <v>131.3307324</v>
       </c>
       <c r="N22">
-        <v>241.7996786666668</v>
+        <v>230.1359342666667</v>
       </c>
       <c r="O22">
-        <v>67.70391002666669</v>
+        <v>64.43806159466669</v>
       </c>
       <c r="P22">
-        <v>174.0957686400001</v>
+        <v>165.697872672</v>
       </c>
       <c r="Q22">
-        <v>619.29576864</v>
+        <v>610.8978726720001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08300704533984302</v>
+        <v>0.08336626375655465</v>
       </c>
       <c r="T22">
-        <v>0.8592851117746654</v>
+        <v>0.8675811491121166</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.28</v>
       </c>
       <c r="W22">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.020604702331664</v>
+        <v>2.752338771444076</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07459870836767818</v>
+        <v>0.07446858046348194</v>
       </c>
       <c r="C23">
-        <v>7794.881739845519</v>
+        <v>7730.944577227652</v>
       </c>
       <c r="D23">
-        <v>9751.139739845519</v>
+        <v>9795.400577227652</v>
       </c>
       <c r="E23">
-        <v>-1716.042</v>
+        <v>-1607.844</v>
       </c>
       <c r="F23">
-        <v>2272.158</v>
+        <v>2380.356</v>
       </c>
       <c r="G23">
         <v>315.9</v>
@@ -3167,28 +3167,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M23">
-        <v>131.3307324</v>
+        <v>137.5845768</v>
       </c>
       <c r="N23">
-        <v>230.1359342666667</v>
+        <v>223.8820898666667</v>
       </c>
       <c r="O23">
-        <v>64.43806159466669</v>
+        <v>62.68698516266669</v>
       </c>
       <c r="P23">
-        <v>165.697872672</v>
+        <v>161.195104704</v>
       </c>
       <c r="Q23">
-        <v>610.8978726720001</v>
+        <v>606.395104704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08336626375655465</v>
+        <v>0.08373469290189992</v>
       </c>
       <c r="T23">
-        <v>0.8675811491121166</v>
+        <v>0.8760899053556563</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.752338771444076</v>
+        <v>2.627232463651164</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07446858046348194</v>
+        <v>0.0743384525592857</v>
       </c>
       <c r="C24">
-        <v>7730.944577227652</v>
+        <v>7667.411050370662</v>
       </c>
       <c r="D24">
-        <v>9795.400577227652</v>
+        <v>9840.065050370662</v>
       </c>
       <c r="E24">
-        <v>-1607.844</v>
+        <v>-1499.646</v>
       </c>
       <c r="F24">
-        <v>2380.356</v>
+        <v>2488.554</v>
       </c>
       <c r="G24">
         <v>315.9</v>
@@ -3249,28 +3249,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M24">
-        <v>137.5845768</v>
+        <v>143.8384212</v>
       </c>
       <c r="N24">
-        <v>223.8820898666667</v>
+        <v>217.6282454666667</v>
       </c>
       <c r="O24">
-        <v>62.68698516266669</v>
+        <v>60.93590873066669</v>
       </c>
       <c r="P24">
-        <v>161.195104704</v>
+        <v>156.692336736</v>
       </c>
       <c r="Q24">
-        <v>606.395104704</v>
+        <v>601.8923367360001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08373469290189992</v>
+        <v>0.08411269163543597</v>
       </c>
       <c r="T24">
-        <v>0.8760899053556563</v>
+        <v>0.8848196682548722</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.627232463651164</v>
+        <v>2.513004965231548</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0743384525592857</v>
+        <v>0.07481312465508946</v>
       </c>
       <c r="C25">
-        <v>7667.411050370662</v>
+        <v>7398.223692766758</v>
       </c>
       <c r="D25">
-        <v>9840.065050370662</v>
+        <v>9679.075692766759</v>
       </c>
       <c r="E25">
-        <v>-1499.646</v>
+        <v>-1391.448</v>
       </c>
       <c r="F25">
-        <v>2488.554</v>
+        <v>2596.752</v>
       </c>
       <c r="G25">
         <v>315.9</v>
@@ -3331,45 +3331,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M25">
-        <v>143.8384212</v>
+        <v>159.1808976</v>
       </c>
       <c r="N25">
-        <v>217.6282454666667</v>
+        <v>202.2857690666667</v>
       </c>
       <c r="O25">
-        <v>60.93590873066669</v>
+        <v>56.64001533866669</v>
       </c>
       <c r="P25">
-        <v>156.692336736</v>
+        <v>145.645753728</v>
       </c>
       <c r="Q25">
-        <v>601.8923367360001</v>
+        <v>590.8457537280001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08411269163543597</v>
+        <v>0.08450063770406507</v>
       </c>
       <c r="T25">
-        <v>0.8848196682548722</v>
+        <v>0.8937791617566994</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.28</v>
       </c>
       <c r="W25">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.513004965231548</v>
+        <v>2.270791735167768</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07481312465508946</v>
+        <v>0.07521219675089322</v>
       </c>
       <c r="C26">
-        <v>7398.223692766758</v>
+        <v>7158.697555162134</v>
       </c>
       <c r="D26">
-        <v>9679.075692766759</v>
+        <v>9547.747555162134</v>
       </c>
       <c r="E26">
-        <v>-1391.448</v>
+        <v>-1283.25</v>
       </c>
       <c r="F26">
-        <v>2596.752</v>
+        <v>2704.95</v>
       </c>
       <c r="G26">
         <v>315.9</v>
@@ -3413,45 +3413,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M26">
-        <v>159.1808976</v>
+        <v>173.387295</v>
       </c>
       <c r="N26">
-        <v>202.2857690666667</v>
+        <v>188.0793716666668</v>
       </c>
       <c r="O26">
-        <v>56.64001533866669</v>
+        <v>52.6622240666667</v>
       </c>
       <c r="P26">
-        <v>145.645753728</v>
+        <v>135.4171476000001</v>
       </c>
       <c r="Q26">
-        <v>590.8457537280001</v>
+        <v>580.6171476000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08450063770406507</v>
+        <v>0.08489892900119096</v>
       </c>
       <c r="T26">
-        <v>0.8937791617566994</v>
+        <v>0.9029775750852417</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.270791735167768</v>
+        <v>2.084735601110028</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07521219675089322</v>
+        <v>0.07512742884669699</v>
       </c>
       <c r="C27">
-        <v>7158.697555162134</v>
+        <v>7078.096333395797</v>
       </c>
       <c r="D27">
-        <v>9547.747555162134</v>
+        <v>9575.344333395797</v>
       </c>
       <c r="E27">
-        <v>-1283.25</v>
+        <v>-1175.052</v>
       </c>
       <c r="F27">
-        <v>2704.95</v>
+        <v>2813.148</v>
       </c>
       <c r="G27">
         <v>315.9</v>
@@ -3495,28 +3495,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M27">
-        <v>173.387295</v>
+        <v>180.3227868</v>
       </c>
       <c r="N27">
-        <v>188.0793716666668</v>
+        <v>181.1438798666668</v>
       </c>
       <c r="O27">
-        <v>52.6622240666667</v>
+        <v>50.7202863626667</v>
       </c>
       <c r="P27">
-        <v>135.4171476000001</v>
+        <v>130.4235935040001</v>
       </c>
       <c r="Q27">
-        <v>580.6171476000001</v>
+        <v>575.623593504</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08489892900119096</v>
+        <v>0.0853079849279689</v>
       </c>
       <c r="T27">
-        <v>0.9029775750852417</v>
+        <v>0.9124245941794203</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.084735601110028</v>
+        <v>2.004553462605796</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07512742884669699</v>
+        <v>0.07731714094250074</v>
       </c>
       <c r="C28">
-        <v>7078.096333395797</v>
+        <v>6304.633443202396</v>
       </c>
       <c r="D28">
-        <v>9575.344333395797</v>
+        <v>8910.079443202396</v>
       </c>
       <c r="E28">
-        <v>-1175.052</v>
+        <v>-1066.854</v>
       </c>
       <c r="F28">
-        <v>2813.148</v>
+        <v>2921.346</v>
       </c>
       <c r="G28">
         <v>315.9</v>
@@ -3577,45 +3577,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M28">
-        <v>180.3227868</v>
+        <v>221.4380268</v>
       </c>
       <c r="N28">
-        <v>181.1438798666668</v>
+        <v>140.0286398666667</v>
       </c>
       <c r="O28">
-        <v>50.7202863626667</v>
+        <v>39.20801916266669</v>
       </c>
       <c r="P28">
-        <v>130.4235935040001</v>
+        <v>100.820620704</v>
       </c>
       <c r="Q28">
-        <v>575.623593504</v>
+        <v>546.0206207040001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0853079849279689</v>
+        <v>0.08572824786643937</v>
       </c>
       <c r="T28">
-        <v>0.9124245941794203</v>
+        <v>0.9221304357145353</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.046152</v>
+        <v>0.054576</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.004553462605796</v>
+        <v>1.632360402999521</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07731714094250074</v>
+        <v>0.0773166130383045</v>
       </c>
       <c r="C29">
-        <v>6304.633443202396</v>
+        <v>6196.584687295379</v>
       </c>
       <c r="D29">
-        <v>8910.079443202396</v>
+        <v>8910.228687295379</v>
       </c>
       <c r="E29">
-        <v>-1066.854</v>
+        <v>-958.6559999999999</v>
       </c>
       <c r="F29">
-        <v>2921.346</v>
+        <v>3029.544</v>
       </c>
       <c r="G29">
         <v>315.9</v>
@@ -3659,28 +3659,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M29">
-        <v>221.4380268</v>
+        <v>229.6394352</v>
       </c>
       <c r="N29">
-        <v>140.0286398666667</v>
+        <v>131.8272314666667</v>
       </c>
       <c r="O29">
-        <v>39.20801916266669</v>
+        <v>36.91162481066669</v>
       </c>
       <c r="P29">
-        <v>100.820620704</v>
+        <v>94.91560665600005</v>
       </c>
       <c r="Q29">
-        <v>546.0206207040001</v>
+        <v>540.1156066560001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08572824786643937</v>
+        <v>0.08616018477542292</v>
       </c>
       <c r="T29">
-        <v>0.9221304357145353</v>
+        <v>0.9321058839589591</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.632360402999521</v>
+        <v>1.57406181717811</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0773166130383045</v>
+        <v>0.07731608513410826</v>
       </c>
       <c r="C30">
-        <v>6196.584687295379</v>
+        <v>6088.535936388136</v>
       </c>
       <c r="D30">
-        <v>8910.228687295379</v>
+        <v>8910.377936388137</v>
       </c>
       <c r="E30">
-        <v>-958.6559999999999</v>
+        <v>-850.4579999999996</v>
       </c>
       <c r="F30">
-        <v>3029.544</v>
+        <v>3137.742</v>
       </c>
       <c r="G30">
         <v>315.9</v>
@@ -3741,28 +3741,28 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M30">
-        <v>229.6394352</v>
+        <v>237.8408436</v>
       </c>
       <c r="N30">
-        <v>131.8272314666667</v>
+        <v>123.6258230666667</v>
       </c>
       <c r="O30">
-        <v>36.91162481066669</v>
+        <v>34.61523045866669</v>
       </c>
       <c r="P30">
-        <v>94.91560665600005</v>
+        <v>89.01059260800004</v>
       </c>
       <c r="Q30">
-        <v>540.1156066560001</v>
+        <v>534.2105926080001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08616018477542292</v>
+        <v>0.08660428892127925</v>
       </c>
       <c r="T30">
-        <v>0.9321058839589591</v>
+        <v>0.9423623307454794</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.57406181717811</v>
+        <v>1.519783823482312</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07731608513410826</v>
+        <v>0.08733024438492518</v>
       </c>
       <c r="C31">
-        <v>6088.535936388136</v>
+        <v>3831.784635980753</v>
       </c>
       <c r="D31">
-        <v>8910.377936388137</v>
+        <v>6761.824635980753</v>
       </c>
       <c r="E31">
-        <v>-850.4580000000001</v>
+        <v>-742.2600000000002</v>
       </c>
       <c r="F31">
-        <v>3137.742</v>
+        <v>3245.94</v>
       </c>
       <c r="G31">
         <v>315.9</v>
@@ -3823,45 +3823,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M31">
-        <v>237.8408436</v>
+        <v>384.968484</v>
       </c>
       <c r="N31">
-        <v>123.6258230666668</v>
+        <v>-23.50181733333324</v>
       </c>
       <c r="O31">
-        <v>34.61523045866669</v>
+        <v>-6.580508853333306</v>
       </c>
       <c r="P31">
-        <v>89.01059260800005</v>
+        <v>-16.92130847999993</v>
       </c>
       <c r="Q31">
-        <v>534.2105926080001</v>
+        <v>428.2786915200001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08660428892127925</v>
+        <v>0.0872920757530084</v>
       </c>
       <c r="T31">
-        <v>0.9423623307454794</v>
+        <v>0.9582465531872609</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.28</v>
+        <v>0.2629063699320038</v>
       </c>
       <c r="W31">
-        <v>0.054576</v>
+        <v>0.08741930452606436</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.519783823482313</v>
+        <v>0.9389513211857279</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08733024438492518</v>
+        <v>0.08805824438492518</v>
       </c>
       <c r="C32">
-        <v>3831.784635980753</v>
+        <v>3607.097926933719</v>
       </c>
       <c r="D32">
-        <v>6761.824635980753</v>
+        <v>6645.335926933719</v>
       </c>
       <c r="E32">
-        <v>-742.2600000000002</v>
+        <v>-634.0619999999999</v>
       </c>
       <c r="F32">
-        <v>3245.94</v>
+        <v>3354.138</v>
       </c>
       <c r="G32">
         <v>315.9</v>
@@ -3905,37 +3905,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M32">
-        <v>384.968484</v>
+        <v>397.8007668</v>
       </c>
       <c r="N32">
-        <v>-23.50181733333324</v>
+        <v>-36.33410013333327</v>
       </c>
       <c r="O32">
-        <v>-6.580508853333306</v>
+        <v>-10.17354803733332</v>
       </c>
       <c r="P32">
-        <v>-16.92130847999993</v>
+        <v>-26.16055209599995</v>
       </c>
       <c r="Q32">
-        <v>428.2786915200001</v>
+        <v>419.039447904</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0872920757530084</v>
+        <v>0.08789341018421142</v>
       </c>
       <c r="T32">
-        <v>0.9582465531872609</v>
+        <v>0.9721341843928734</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.2629063699320038</v>
+        <v>0.254425519289036</v>
       </c>
       <c r="W32">
-        <v>0.08741930452606436</v>
+        <v>0.08842513341232035</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9389513211857279</v>
+        <v>0.9086625688894141</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08805824438492518</v>
+        <v>0.08878624438492516</v>
       </c>
       <c r="C33">
-        <v>3607.097926933719</v>
+        <v>3386.356841953163</v>
       </c>
       <c r="D33">
-        <v>6645.335926933719</v>
+        <v>6532.792841953163</v>
       </c>
       <c r="E33">
-        <v>-634.0619999999999</v>
+        <v>-525.864</v>
       </c>
       <c r="F33">
-        <v>3354.138</v>
+        <v>3462.336</v>
       </c>
       <c r="G33">
         <v>315.9</v>
@@ -3987,37 +3987,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M33">
-        <v>397.8007668</v>
+        <v>410.6330496</v>
       </c>
       <c r="N33">
-        <v>-36.33410013333327</v>
+        <v>-49.16638293333324</v>
       </c>
       <c r="O33">
-        <v>-10.17354803733332</v>
+        <v>-13.76658722133331</v>
       </c>
       <c r="P33">
-        <v>-26.16055209599995</v>
+        <v>-35.39979571199993</v>
       </c>
       <c r="Q33">
-        <v>419.039447904</v>
+        <v>409.800204288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08789341018421142</v>
+        <v>0.08851243092221452</v>
       </c>
       <c r="T33">
-        <v>0.9721341843928734</v>
+        <v>0.9864302753398272</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.254425519289036</v>
+        <v>0.2464747218112536</v>
       </c>
       <c r="W33">
-        <v>0.08842513341232035</v>
+        <v>0.08936809799318533</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9086625688894141</v>
+        <v>0.88026686361162</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08878624438492516</v>
+        <v>0.08951424438492518</v>
       </c>
       <c r="C34">
-        <v>3386.356841953163</v>
+        <v>3169.364254379732</v>
       </c>
       <c r="D34">
-        <v>6532.792841953163</v>
+        <v>6423.998254379732</v>
       </c>
       <c r="E34">
-        <v>-525.864</v>
+        <v>-417.6659999999997</v>
       </c>
       <c r="F34">
-        <v>3462.336</v>
+        <v>3570.534</v>
       </c>
       <c r="G34">
         <v>315.9</v>
@@ -4069,37 +4069,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M34">
-        <v>410.6330496</v>
+        <v>423.4653324000001</v>
       </c>
       <c r="N34">
-        <v>-49.16638293333324</v>
+        <v>-61.99866573333333</v>
       </c>
       <c r="O34">
-        <v>-13.76658722133331</v>
+        <v>-17.35962640533333</v>
       </c>
       <c r="P34">
-        <v>-35.39979571199993</v>
+        <v>-44.639039328</v>
       </c>
       <c r="Q34">
-        <v>409.800204288</v>
+        <v>400.560960672</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08851243092221452</v>
+        <v>0.08914992989120279</v>
       </c>
       <c r="T34">
-        <v>0.9864302753398272</v>
+        <v>1.001153115270273</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.2464747218112536</v>
+        <v>0.2390057908472762</v>
       </c>
       <c r="W34">
-        <v>0.08936809799318533</v>
+        <v>0.09025391320551306</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.88026686361162</v>
+        <v>0.8535921101688434</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08951424438492518</v>
+        <v>0.09024224438492517</v>
       </c>
       <c r="C35">
-        <v>3169.364254379732</v>
+        <v>2955.935953932198</v>
       </c>
       <c r="D35">
-        <v>6423.998254379732</v>
+        <v>6318.767953932198</v>
       </c>
       <c r="E35">
-        <v>-417.6659999999997</v>
+        <v>-309.4679999999998</v>
       </c>
       <c r="F35">
-        <v>3570.534</v>
+        <v>3678.732</v>
       </c>
       <c r="G35">
         <v>315.9</v>
@@ -4151,37 +4151,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M35">
-        <v>423.4653324000001</v>
+        <v>436.2976152000001</v>
       </c>
       <c r="N35">
-        <v>-61.99866573333333</v>
+        <v>-74.8309485333333</v>
       </c>
       <c r="O35">
-        <v>-17.35962640533333</v>
+        <v>-20.95266558933332</v>
       </c>
       <c r="P35">
-        <v>-44.639039328</v>
+        <v>-53.87828294399998</v>
       </c>
       <c r="Q35">
-        <v>400.560960672</v>
+        <v>391.321717056</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08914992989120279</v>
+        <v>0.08980674701076648</v>
       </c>
       <c r="T35">
-        <v>1.001153115270273</v>
+        <v>1.016322101865277</v>
       </c>
       <c r="U35">
         <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.2390057908472762</v>
+        <v>0.2319762087635328</v>
       </c>
       <c r="W35">
-        <v>0.09025391320551306</v>
+        <v>0.09108762164064503</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8535921101688434</v>
+        <v>0.8284864598697599</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09024224438492517</v>
+        <v>0.09097024438492518</v>
       </c>
       <c r="C36">
-        <v>2955.935953932198</v>
+        <v>2745.899605853704</v>
       </c>
       <c r="D36">
-        <v>6318.767953932198</v>
+        <v>6216.929605853705</v>
       </c>
       <c r="E36">
-        <v>-309.4679999999998</v>
+        <v>-201.2699999999995</v>
       </c>
       <c r="F36">
-        <v>3678.732</v>
+        <v>3786.93</v>
       </c>
       <c r="G36">
         <v>315.9</v>
@@ -4233,37 +4233,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M36">
-        <v>436.2976152000001</v>
+        <v>449.1298980000001</v>
       </c>
       <c r="N36">
-        <v>-74.8309485333333</v>
+        <v>-87.66323133333333</v>
       </c>
       <c r="O36">
-        <v>-20.95266558933332</v>
+        <v>-24.54570477333333</v>
       </c>
       <c r="P36">
-        <v>-53.87828294399998</v>
+        <v>-63.11752655999999</v>
       </c>
       <c r="Q36">
-        <v>391.321717056</v>
+        <v>382.08247344</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08980674701076648</v>
+        <v>0.0904837738878552</v>
       </c>
       <c r="T36">
-        <v>1.016322101865277</v>
+        <v>1.031957826509358</v>
       </c>
       <c r="U36">
         <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.2319762087635328</v>
+        <v>0.2253483170845747</v>
       </c>
       <c r="W36">
-        <v>0.09108762164064503</v>
+        <v>0.09187368959376944</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8284864598697599</v>
+        <v>0.8048154181591952</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09097024438492518</v>
+        <v>0.1223083050284441</v>
       </c>
       <c r="C37">
-        <v>2745.899605853704</v>
+        <v>91.22620122541912</v>
       </c>
       <c r="D37">
-        <v>6216.929605853705</v>
+        <v>3670.454201225419</v>
       </c>
       <c r="E37">
-        <v>-201.2699999999995</v>
+        <v>-93.07199999999966</v>
       </c>
       <c r="F37">
-        <v>3786.93</v>
+        <v>3895.128</v>
       </c>
       <c r="G37">
         <v>315.9</v>
@@ -4315,45 +4315,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M37">
-        <v>449.1298980000001</v>
+        <v>782.1417024000001</v>
       </c>
       <c r="N37">
-        <v>-87.66323133333333</v>
+        <v>-420.6750357333333</v>
       </c>
       <c r="O37">
-        <v>-24.54570477333333</v>
+        <v>-117.7890100053334</v>
       </c>
       <c r="P37">
-        <v>-63.11752655999999</v>
+        <v>-302.886025728</v>
       </c>
       <c r="Q37">
-        <v>382.08247344</v>
+        <v>142.313974272</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0904837738878552</v>
+        <v>0.09277267761035116</v>
       </c>
       <c r="T37">
-        <v>1.031957826509358</v>
+        <v>1.084819344349911</v>
       </c>
       <c r="U37">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.2253483170845747</v>
+        <v>0.1294019566481393</v>
       </c>
       <c r="W37">
-        <v>0.09187368959376944</v>
+        <v>0.1748160871050536</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8048154181591952</v>
+        <v>0.4621498451719261</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.122308305028444</v>
+        <v>0.123858305028444</v>
       </c>
       <c r="C38">
-        <v>91.22620122542094</v>
+        <v>-89.85583090704995</v>
       </c>
       <c r="D38">
-        <v>3670.454201225421</v>
+        <v>3597.57016909295</v>
       </c>
       <c r="E38">
-        <v>-93.07200000000012</v>
+        <v>15.12599999999975</v>
       </c>
       <c r="F38">
-        <v>3895.128</v>
+        <v>4003.326</v>
       </c>
       <c r="G38">
         <v>315.9</v>
@@ -4397,37 +4397,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M38">
-        <v>782.1417024</v>
+        <v>803.8678607999999</v>
       </c>
       <c r="N38">
-        <v>-420.6750357333332</v>
+        <v>-442.4011941333331</v>
       </c>
       <c r="O38">
-        <v>-117.7890100053333</v>
+        <v>-123.8723343573333</v>
       </c>
       <c r="P38">
-        <v>-302.8860257279999</v>
+        <v>-318.5288597759999</v>
       </c>
       <c r="Q38">
-        <v>142.3139742720001</v>
+        <v>126.6711402240001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09277267761035116</v>
+        <v>0.09351827566765832</v>
       </c>
       <c r="T38">
-        <v>1.084819344349911</v>
+        <v>1.102038699022132</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1294019566481394</v>
+        <v>0.1259046064684599</v>
       </c>
       <c r="W38">
-        <v>0.1748160871050536</v>
+        <v>0.1755183550211332</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4621498451719261</v>
+        <v>0.4496593088159282</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.123858305028444</v>
+        <v>0.1254083050284441</v>
       </c>
       <c r="C39">
-        <v>-89.85583090704995</v>
+        <v>-268.0997106692403</v>
       </c>
       <c r="D39">
-        <v>3597.57016909295</v>
+        <v>3527.524289330759</v>
       </c>
       <c r="E39">
-        <v>15.12599999999975</v>
+        <v>123.3239999999996</v>
       </c>
       <c r="F39">
-        <v>4003.326</v>
+        <v>4111.523999999999</v>
       </c>
       <c r="G39">
         <v>315.9</v>
@@ -4479,37 +4479,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M39">
-        <v>803.8678607999999</v>
+        <v>825.5940191999999</v>
       </c>
       <c r="N39">
-        <v>-442.4011941333331</v>
+        <v>-464.1273525333332</v>
       </c>
       <c r="O39">
-        <v>-123.8723343573333</v>
+        <v>-129.9556587093333</v>
       </c>
       <c r="P39">
-        <v>-318.5288597759999</v>
+        <v>-334.1716938239999</v>
       </c>
       <c r="Q39">
-        <v>126.6711402240001</v>
+        <v>111.0283061760001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09351827566765832</v>
+        <v>0.09428792527520119</v>
       </c>
       <c r="T39">
-        <v>1.102038699022132</v>
+        <v>1.119813516748295</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1259046064684599</v>
+        <v>0.1225913273508688</v>
       </c>
       <c r="W39">
-        <v>0.1755183550211332</v>
+        <v>0.1761836614679455</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4496593088159282</v>
+        <v>0.4378261691102459</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1254083050284441</v>
+        <v>0.126958305028444</v>
       </c>
       <c r="C40">
-        <v>-268.0997106692403</v>
+        <v>-443.6680512221446</v>
       </c>
       <c r="D40">
-        <v>3527.524289330759</v>
+        <v>3460.153948777855</v>
       </c>
       <c r="E40">
-        <v>123.3239999999996</v>
+        <v>231.5219999999999</v>
       </c>
       <c r="F40">
-        <v>4111.523999999999</v>
+        <v>4219.722</v>
       </c>
       <c r="G40">
         <v>315.9</v>
@@ -4561,37 +4561,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M40">
-        <v>825.5940191999999</v>
+        <v>847.3201776</v>
       </c>
       <c r="N40">
-        <v>-464.1273525333332</v>
+        <v>-485.8535109333332</v>
       </c>
       <c r="O40">
-        <v>-129.9556587093333</v>
+        <v>-136.0389830613333</v>
       </c>
       <c r="P40">
-        <v>-334.1716938239999</v>
+        <v>-349.8145278719999</v>
       </c>
       <c r="Q40">
-        <v>111.0283061760001</v>
+        <v>95.38547212800012</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09428792527520119</v>
+        <v>0.09508280929610613</v>
       </c>
       <c r="T40">
-        <v>1.119813516748295</v>
+        <v>1.138171115383513</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1225913273508688</v>
+        <v>0.1194479599828979</v>
       </c>
       <c r="W40">
-        <v>0.1761836614679455</v>
+        <v>0.1768148496354341</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4378261691102459</v>
+        <v>0.4265998570817781</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.126958305028444</v>
+        <v>0.1285083050284441</v>
       </c>
       <c r="C41">
-        <v>-443.6680512221446</v>
+        <v>-616.711275879587</v>
       </c>
       <c r="D41">
-        <v>3460.153948777855</v>
+        <v>3395.308724120413</v>
       </c>
       <c r="E41">
-        <v>231.5219999999999</v>
+        <v>339.7200000000003</v>
       </c>
       <c r="F41">
-        <v>4219.722</v>
+        <v>4327.92</v>
       </c>
       <c r="G41">
         <v>315.9</v>
@@ -4643,37 +4643,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M41">
-        <v>847.3201776</v>
+        <v>869.046336</v>
       </c>
       <c r="N41">
-        <v>-485.8535109333332</v>
+        <v>-507.5796693333332</v>
       </c>
       <c r="O41">
-        <v>-136.0389830613333</v>
+        <v>-142.1223074133333</v>
       </c>
       <c r="P41">
-        <v>-349.8145278719999</v>
+        <v>-365.4573619199999</v>
       </c>
       <c r="Q41">
-        <v>95.38547212800012</v>
+        <v>79.74263808000006</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09508280929610613</v>
+        <v>0.09590418945104123</v>
       </c>
       <c r="T41">
-        <v>1.138171115383513</v>
+        <v>1.157140633973239</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1194479599828979</v>
+        <v>0.1164617609833254</v>
       </c>
       <c r="W41">
-        <v>0.1768148496354341</v>
+        <v>0.1774144783945483</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4265998570817781</v>
+        <v>0.4159348606547335</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1285083050284441</v>
+        <v>0.1300583050284441</v>
       </c>
       <c r="C42">
-        <v>-616.711275879587</v>
+        <v>-787.3687393189489</v>
       </c>
       <c r="D42">
-        <v>3395.308724120413</v>
+        <v>3332.849260681051</v>
       </c>
       <c r="E42">
-        <v>339.7200000000003</v>
+        <v>447.9180000000006</v>
       </c>
       <c r="F42">
-        <v>4327.92</v>
+        <v>4436.118</v>
       </c>
       <c r="G42">
         <v>315.9</v>
@@ -4725,37 +4725,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M42">
-        <v>869.046336</v>
+        <v>890.7724944000001</v>
       </c>
       <c r="N42">
-        <v>-507.5796693333332</v>
+        <v>-529.3058277333334</v>
       </c>
       <c r="O42">
-        <v>-142.1223074133333</v>
+        <v>-148.2056317653334</v>
       </c>
       <c r="P42">
-        <v>-365.4573619199999</v>
+        <v>-381.1001959680001</v>
       </c>
       <c r="Q42">
-        <v>79.74263808000006</v>
+        <v>64.09980403199989</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09590418945104123</v>
+        <v>0.09675341300105889</v>
       </c>
       <c r="T42">
-        <v>1.157140633973239</v>
+        <v>1.176753187091429</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1164617609833254</v>
+        <v>0.1136212302276345</v>
       </c>
       <c r="W42">
-        <v>0.1774144783945483</v>
+        <v>0.177984856970291</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4159348606547335</v>
+        <v>0.4057901079558375</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1300583050284441</v>
+        <v>0.1316083050284441</v>
       </c>
       <c r="C43">
-        <v>-787.3687393189489</v>
+        <v>-955.7697272738224</v>
       </c>
       <c r="D43">
-        <v>3332.849260681051</v>
+        <v>3272.646272726177</v>
       </c>
       <c r="E43">
-        <v>447.9180000000006</v>
+        <v>556.116</v>
       </c>
       <c r="F43">
-        <v>4436.118</v>
+        <v>4544.316</v>
       </c>
       <c r="G43">
         <v>315.9</v>
@@ -4807,37 +4807,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M43">
-        <v>890.7724944000001</v>
+        <v>912.4986527999999</v>
       </c>
       <c r="N43">
-        <v>-529.3058277333334</v>
+        <v>-551.0319861333332</v>
       </c>
       <c r="O43">
-        <v>-148.2056317653334</v>
+        <v>-154.2889561173333</v>
       </c>
       <c r="P43">
-        <v>-381.1001959680001</v>
+        <v>-396.7430300159999</v>
       </c>
       <c r="Q43">
-        <v>64.09980403199989</v>
+        <v>48.45696998400007</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09675341300105889</v>
+        <v>0.0976319201217668</v>
       </c>
       <c r="T43">
-        <v>1.176753187091429</v>
+        <v>1.19704203514473</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1136212302276345</v>
+        <v>0.1109159628412623</v>
       </c>
       <c r="W43">
-        <v>0.177984856970291</v>
+        <v>0.1785280746614746</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4057901079558375</v>
+        <v>0.3961284387187938</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1316083050284441</v>
+        <v>0.1331583050284441</v>
       </c>
       <c r="C44">
-        <v>-955.7697272738224</v>
+        <v>-1122.034349801284</v>
       </c>
       <c r="D44">
-        <v>3272.646272726177</v>
+        <v>3214.579650198715</v>
       </c>
       <c r="E44">
-        <v>556.116</v>
+        <v>664.3139999999994</v>
       </c>
       <c r="F44">
-        <v>4544.316</v>
+        <v>4652.513999999999</v>
       </c>
       <c r="G44">
         <v>315.9</v>
@@ -4889,37 +4889,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M44">
-        <v>912.4986527999999</v>
+        <v>934.2248111999999</v>
       </c>
       <c r="N44">
-        <v>-551.0319861333332</v>
+        <v>-572.7581445333331</v>
       </c>
       <c r="O44">
-        <v>-154.2889561173333</v>
+        <v>-160.3722804693333</v>
       </c>
       <c r="P44">
-        <v>-396.7430300159999</v>
+        <v>-412.3858640639997</v>
       </c>
       <c r="Q44">
-        <v>48.45696998400007</v>
+        <v>32.81413593600024</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0976319201217668</v>
+        <v>0.09854125205372762</v>
       </c>
       <c r="T44">
-        <v>1.19704203514473</v>
+        <v>1.218042772603409</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1109159628412623</v>
+        <v>0.1083365218449539</v>
       </c>
       <c r="W44">
-        <v>0.1785280746614746</v>
+        <v>0.1790460264135333</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3961284387187938</v>
+        <v>0.3869161494462638</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1331583050284441</v>
+        <v>0.1347083050284441</v>
       </c>
       <c r="C45">
-        <v>-1122.034349801284</v>
+        <v>-1286.274341111477</v>
       </c>
       <c r="D45">
-        <v>3214.579650198715</v>
+        <v>3158.537658888523</v>
       </c>
       <c r="E45">
-        <v>664.3139999999994</v>
+        <v>772.5119999999997</v>
       </c>
       <c r="F45">
-        <v>4652.513999999999</v>
+        <v>4760.712</v>
       </c>
       <c r="G45">
         <v>315.9</v>
@@ -4971,37 +4971,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M45">
-        <v>934.2248111999999</v>
+        <v>955.9509695999999</v>
       </c>
       <c r="N45">
-        <v>-572.7581445333331</v>
+        <v>-594.4843029333331</v>
       </c>
       <c r="O45">
-        <v>-160.3722804693333</v>
+        <v>-166.4556048213333</v>
       </c>
       <c r="P45">
-        <v>-412.3858640639997</v>
+        <v>-428.0286981119998</v>
       </c>
       <c r="Q45">
-        <v>32.81413593600024</v>
+        <v>17.17130188800019</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09854125205372762</v>
+        <v>0.0994830601261156</v>
       </c>
       <c r="T45">
-        <v>1.218042772603409</v>
+        <v>1.239793536399899</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1083365218449539</v>
+        <v>0.1058743281666595</v>
       </c>
       <c r="W45">
-        <v>0.1790460264135333</v>
+        <v>0.1795404349041348</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3869161494462638</v>
+        <v>0.3781226005952124</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1347083050284441</v>
+        <v>0.1362583050284441</v>
       </c>
       <c r="C46">
-        <v>-1286.274341111477</v>
+        <v>-1448.593777166882</v>
       </c>
       <c r="D46">
-        <v>3158.537658888523</v>
+        <v>3104.416222833117</v>
       </c>
       <c r="E46">
-        <v>772.5119999999997</v>
+        <v>880.71</v>
       </c>
       <c r="F46">
-        <v>4760.712</v>
+        <v>4868.91</v>
       </c>
       <c r="G46">
         <v>315.9</v>
@@ -5053,37 +5053,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M46">
-        <v>955.9509695999999</v>
+        <v>977.677128</v>
       </c>
       <c r="N46">
-        <v>-594.4843029333331</v>
+        <v>-616.2104613333333</v>
       </c>
       <c r="O46">
-        <v>-166.4556048213333</v>
+        <v>-172.5389291733333</v>
       </c>
       <c r="P46">
-        <v>-428.0286981119998</v>
+        <v>-443.67153216</v>
       </c>
       <c r="Q46">
-        <v>17.17130188800019</v>
+        <v>1.528467840000019</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0994830601261156</v>
+        <v>0.1004591157647723</v>
       </c>
       <c r="T46">
-        <v>1.239793536399899</v>
+        <v>1.262335237061715</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1058743281666595</v>
+        <v>0.1035215653185115</v>
       </c>
       <c r="W46">
-        <v>0.1795404349041348</v>
+        <v>0.1800128696840429</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3781226005952124</v>
+        <v>0.3697198761375409</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1362583050284441</v>
+        <v>0.137808305028444</v>
       </c>
       <c r="C47">
-        <v>-1448.593777166882</v>
+        <v>-1609.089720748212</v>
       </c>
       <c r="D47">
-        <v>3104.416222833117</v>
+        <v>3052.118279251788</v>
       </c>
       <c r="E47">
-        <v>880.71</v>
+        <v>988.9080000000004</v>
       </c>
       <c r="F47">
-        <v>4868.91</v>
+        <v>4977.108</v>
       </c>
       <c r="G47">
         <v>315.9</v>
@@ -5135,37 +5135,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M47">
-        <v>977.677128</v>
+        <v>999.4032864000001</v>
       </c>
       <c r="N47">
-        <v>-616.2104613333333</v>
+        <v>-637.9366197333334</v>
       </c>
       <c r="O47">
-        <v>-172.5389291733333</v>
+        <v>-178.6222535253333</v>
       </c>
       <c r="P47">
-        <v>-443.67153216</v>
+        <v>-459.314366208</v>
       </c>
       <c r="Q47">
-        <v>1.528467840000019</v>
+        <v>-14.11436620800004</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1004591157647723</v>
+        <v>0.101471321612268</v>
       </c>
       <c r="T47">
-        <v>1.262335237061715</v>
+        <v>1.285711815525821</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1035215653185115</v>
+        <v>0.1012710965072395</v>
       </c>
       <c r="W47">
-        <v>0.1800128696840429</v>
+        <v>0.1804647638213463</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3697198761375409</v>
+        <v>0.3616824875258552</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.137808305028444</v>
+        <v>0.1393583050284441</v>
       </c>
       <c r="C48">
-        <v>-1609.089720748212</v>
+        <v>-1767.852802398655</v>
       </c>
       <c r="D48">
-        <v>3052.118279251788</v>
+        <v>3001.553197601345</v>
       </c>
       <c r="E48">
-        <v>988.9080000000004</v>
+        <v>1097.106</v>
       </c>
       <c r="F48">
-        <v>4977.108</v>
+        <v>5085.306</v>
       </c>
       <c r="G48">
         <v>315.9</v>
@@ -5217,37 +5217,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M48">
-        <v>999.4032864000001</v>
+        <v>1021.1294448</v>
       </c>
       <c r="N48">
-        <v>-637.9366197333334</v>
+        <v>-659.6627781333332</v>
       </c>
       <c r="O48">
-        <v>-178.6222535253333</v>
+        <v>-184.7055778773333</v>
       </c>
       <c r="P48">
-        <v>-459.314366208</v>
+        <v>-474.9572002559999</v>
       </c>
       <c r="Q48">
-        <v>-14.11436620800004</v>
+        <v>-29.75720025599986</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.101471321612268</v>
+        <v>0.1025217239068391</v>
       </c>
       <c r="T48">
-        <v>1.285711815525821</v>
+        <v>1.309970529026308</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1012710965072395</v>
+        <v>0.09911639232623438</v>
       </c>
       <c r="W48">
-        <v>0.1804647638213463</v>
+        <v>0.1808974284208922</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3616824875258552</v>
+        <v>0.3539871154508372</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1393583050284441</v>
+        <v>0.140908305028444</v>
       </c>
       <c r="C49">
-        <v>-1767.852802398655</v>
+        <v>-1924.967744561493</v>
       </c>
       <c r="D49">
-        <v>3001.553197601345</v>
+        <v>2952.636255438507</v>
       </c>
       <c r="E49">
-        <v>1097.106</v>
+        <v>1205.304</v>
       </c>
       <c r="F49">
-        <v>5085.306</v>
+        <v>5193.504</v>
       </c>
       <c r="G49">
         <v>315.9</v>
@@ -5299,37 +5299,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M49">
-        <v>1021.1294448</v>
+        <v>1042.8556032</v>
       </c>
       <c r="N49">
-        <v>-659.6627781333332</v>
+        <v>-681.3889365333332</v>
       </c>
       <c r="O49">
-        <v>-184.7055778773333</v>
+        <v>-190.7889022293333</v>
       </c>
       <c r="P49">
-        <v>-474.9572002559999</v>
+        <v>-490.6000343039999</v>
       </c>
       <c r="Q49">
-        <v>-29.75720025599986</v>
+        <v>-45.40003430399992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1025217239068391</v>
+        <v>0.103612526289663</v>
       </c>
       <c r="T49">
-        <v>1.309970529026308</v>
+        <v>1.335162269969121</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.09911639232623438</v>
+        <v>0.09705146748610452</v>
       </c>
       <c r="W49">
-        <v>0.1808974284208922</v>
+        <v>0.1813120653287902</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3539871154508372</v>
+        <v>0.3466123838789446</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.140908305028444</v>
+        <v>0.1424583050284441</v>
       </c>
       <c r="C50">
-        <v>-1924.967744561493</v>
+        <v>-2080.513835287716</v>
       </c>
       <c r="D50">
-        <v>2952.636255438507</v>
+        <v>2905.288164712284</v>
       </c>
       <c r="E50">
-        <v>1205.304</v>
+        <v>1313.501999999999</v>
       </c>
       <c r="F50">
-        <v>5193.504</v>
+        <v>5301.701999999999</v>
       </c>
       <c r="G50">
         <v>315.9</v>
@@ -5381,37 +5381,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M50">
-        <v>1042.8556032</v>
+        <v>1064.5817616</v>
       </c>
       <c r="N50">
-        <v>-681.3889365333332</v>
+        <v>-703.1150949333332</v>
       </c>
       <c r="O50">
-        <v>-190.7889022293333</v>
+        <v>-196.8722265813333</v>
       </c>
       <c r="P50">
-        <v>-490.6000343039999</v>
+        <v>-506.2428683519999</v>
       </c>
       <c r="Q50">
-        <v>-45.40003430399992</v>
+        <v>-61.04286835199991</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.103612526289663</v>
+        <v>0.1047461052365191</v>
       </c>
       <c r="T50">
-        <v>1.335162269969121</v>
+        <v>1.361341922321457</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.09705146748610452</v>
+        <v>0.09507082529251054</v>
       </c>
       <c r="W50">
-        <v>0.1813120653287902</v>
+        <v>0.1817097782812639</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3466123838789446</v>
+        <v>0.3395386617589661</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1424583050284441</v>
+        <v>0.144008305028444</v>
       </c>
       <c r="C51">
-        <v>-2080.513835287716</v>
+        <v>-2234.56535708508</v>
       </c>
       <c r="D51">
-        <v>2905.288164712284</v>
+        <v>2859.43464291492</v>
       </c>
       <c r="E51">
-        <v>1313.501999999999</v>
+        <v>1421.7</v>
       </c>
       <c r="F51">
-        <v>5301.701999999999</v>
+        <v>5409.9</v>
       </c>
       <c r="G51">
         <v>315.9</v>
@@ -5463,37 +5463,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M51">
-        <v>1064.5817616</v>
+        <v>1086.30792</v>
       </c>
       <c r="N51">
-        <v>-703.1150949333332</v>
+        <v>-724.8412533333333</v>
       </c>
       <c r="O51">
-        <v>-196.8722265813333</v>
+        <v>-202.9555509333333</v>
       </c>
       <c r="P51">
-        <v>-506.2428683519999</v>
+        <v>-521.8857023999999</v>
       </c>
       <c r="Q51">
-        <v>-61.04286835199991</v>
+        <v>-76.68570239999991</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1047461052365191</v>
+        <v>0.1059250273412495</v>
       </c>
       <c r="T51">
-        <v>1.361341922321457</v>
+        <v>1.388568760767886</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.09507082529251054</v>
+        <v>0.09316940878666033</v>
       </c>
       <c r="W51">
-        <v>0.1817097782812639</v>
+        <v>0.1820915827156386</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3395386617589661</v>
+        <v>0.3327478885237868</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.144008305028444</v>
+        <v>0.1455583050284441</v>
       </c>
       <c r="C52">
-        <v>-2234.56535708508</v>
+        <v>-2387.191975787598</v>
       </c>
       <c r="D52">
-        <v>2859.43464291492</v>
+        <v>2815.006024212401</v>
       </c>
       <c r="E52">
-        <v>1421.7</v>
+        <v>1529.898</v>
       </c>
       <c r="F52">
-        <v>5409.9</v>
+        <v>5518.098</v>
       </c>
       <c r="G52">
         <v>315.9</v>
@@ -5545,37 +5545,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M52">
-        <v>1086.30792</v>
+        <v>1108.0340784</v>
       </c>
       <c r="N52">
-        <v>-724.8412533333333</v>
+        <v>-746.5674117333333</v>
       </c>
       <c r="O52">
-        <v>-202.9555509333333</v>
+        <v>-209.0388752853333</v>
       </c>
       <c r="P52">
-        <v>-521.8857023999999</v>
+        <v>-537.528536448</v>
       </c>
       <c r="Q52">
-        <v>-76.68570239999991</v>
+        <v>-92.32853644799997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1059250273412495</v>
+        <v>0.1071520687155607</v>
       </c>
       <c r="T52">
-        <v>1.388568760767886</v>
+        <v>1.416906898742741</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.09316940878666033</v>
+        <v>0.09134255763398071</v>
       </c>
       <c r="W52">
-        <v>0.1820915827156386</v>
+        <v>0.1824584144270967</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3327478885237868</v>
+        <v>0.3262234201213596</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1455583050284441</v>
+        <v>0.147108305028444</v>
       </c>
       <c r="C53">
-        <v>-2387.191975787598</v>
+        <v>-2538.45909372718</v>
       </c>
       <c r="D53">
-        <v>2815.006024212401</v>
+        <v>2771.936906272819</v>
       </c>
       <c r="E53">
-        <v>1529.898</v>
+        <v>1638.096</v>
       </c>
       <c r="F53">
-        <v>5518.098</v>
+        <v>5626.295999999999</v>
       </c>
       <c r="G53">
         <v>315.9</v>
@@ -5627,37 +5627,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M53">
-        <v>1108.0340784</v>
+        <v>1129.7602368</v>
       </c>
       <c r="N53">
-        <v>-746.5674117333333</v>
+        <v>-768.2935701333331</v>
       </c>
       <c r="O53">
-        <v>-209.0388752853333</v>
+        <v>-215.1221996373333</v>
       </c>
       <c r="P53">
-        <v>-537.528536448</v>
+        <v>-553.1713704959998</v>
       </c>
       <c r="Q53">
-        <v>-92.32853644799997</v>
+        <v>-107.9713704959998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1071520687155607</v>
+        <v>0.1084302368138015</v>
       </c>
       <c r="T53">
-        <v>1.416906898742741</v>
+        <v>1.446425792466548</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09134255763398071</v>
+        <v>0.08958596998717341</v>
       </c>
       <c r="W53">
-        <v>0.1824584144270967</v>
+        <v>0.1828111372265756</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3262234201213596</v>
+        <v>0.3199498928113335</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.147108305028444</v>
+        <v>0.148658305028444</v>
       </c>
       <c r="C54">
-        <v>-2538.45909372718</v>
+        <v>-2688.428170973054</v>
       </c>
       <c r="D54">
-        <v>2771.936906272819</v>
+        <v>2730.165829026945</v>
       </c>
       <c r="E54">
-        <v>1638.096</v>
+        <v>1746.294</v>
       </c>
       <c r="F54">
-        <v>5626.295999999999</v>
+        <v>5734.494</v>
       </c>
       <c r="G54">
         <v>315.9</v>
@@ -5709,37 +5709,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M54">
-        <v>1129.7602368</v>
+        <v>1151.4863952</v>
       </c>
       <c r="N54">
-        <v>-768.2935701333331</v>
+        <v>-790.0197285333334</v>
       </c>
       <c r="O54">
-        <v>-215.1221996373333</v>
+        <v>-221.2055239893334</v>
       </c>
       <c r="P54">
-        <v>-553.1713704959998</v>
+        <v>-568.8142045439999</v>
       </c>
       <c r="Q54">
-        <v>-107.9713704959998</v>
+        <v>-123.614204544</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1084302368138015</v>
+        <v>0.1097627950438824</v>
       </c>
       <c r="T54">
-        <v>1.446425792466548</v>
+        <v>1.477200809327539</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.08958596998717341</v>
+        <v>0.08789566866666068</v>
       </c>
       <c r="W54">
-        <v>0.1828111372265756</v>
+        <v>0.1831505497317346</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3199498928113335</v>
+        <v>0.313913102380931</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.148658305028444</v>
+        <v>0.1502083050284441</v>
       </c>
       <c r="C55">
-        <v>-2688.428170973054</v>
+        <v>-2837.157017957296</v>
       </c>
       <c r="D55">
-        <v>2730.165829026945</v>
+        <v>2689.634982042704</v>
       </c>
       <c r="E55">
-        <v>1746.294</v>
+        <v>1854.492</v>
       </c>
       <c r="F55">
-        <v>5734.494</v>
+        <v>5842.692</v>
       </c>
       <c r="G55">
         <v>315.9</v>
@@ -5791,37 +5791,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M55">
-        <v>1151.4863952</v>
+        <v>1173.2125536</v>
       </c>
       <c r="N55">
-        <v>-790.0197285333334</v>
+        <v>-811.7458869333334</v>
       </c>
       <c r="O55">
-        <v>-221.2055239893334</v>
+        <v>-227.2888483413334</v>
       </c>
       <c r="P55">
-        <v>-568.8142045439999</v>
+        <v>-584.457038592</v>
       </c>
       <c r="Q55">
-        <v>-123.614204544</v>
+        <v>-139.257038592</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1097627950438824</v>
+        <v>0.1111532905883147</v>
       </c>
       <c r="T55">
-        <v>1.477200809327539</v>
+        <v>1.509313870399877</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08789566866666068</v>
+        <v>0.08626797109875955</v>
       </c>
       <c r="W55">
-        <v>0.1831505497317346</v>
+        <v>0.1834773914033691</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.313913102380931</v>
+        <v>0.308099896781284</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1502083050284441</v>
+        <v>0.151758305028444</v>
       </c>
       <c r="C56">
-        <v>-2837.157017957296</v>
+        <v>-2984.700062416501</v>
       </c>
       <c r="D56">
-        <v>2689.634982042704</v>
+        <v>2650.289937583499</v>
       </c>
       <c r="E56">
-        <v>1854.492</v>
+        <v>1962.690000000001</v>
       </c>
       <c r="F56">
-        <v>5842.692</v>
+        <v>5950.89</v>
       </c>
       <c r="G56">
         <v>315.9</v>
@@ -5873,37 +5873,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M56">
-        <v>1173.2125536</v>
+        <v>1194.938712</v>
       </c>
       <c r="N56">
-        <v>-811.7458869333334</v>
+        <v>-833.4720453333334</v>
       </c>
       <c r="O56">
-        <v>-227.2888483413334</v>
+        <v>-233.3721726933334</v>
       </c>
       <c r="P56">
-        <v>-584.457038592</v>
+        <v>-600.0998726400001</v>
       </c>
       <c r="Q56">
-        <v>-139.257038592</v>
+        <v>-154.8998726400001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1111532905883147</v>
+        <v>0.1126055859347216</v>
       </c>
       <c r="T56">
-        <v>1.509313870399877</v>
+        <v>1.542854178630985</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.08626797109875955</v>
+        <v>0.08469946253332757</v>
       </c>
       <c r="W56">
-        <v>0.1834773914033691</v>
+        <v>0.1837923479233078</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.308099896781284</v>
+        <v>0.3024980804761698</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.151758305028444</v>
+        <v>0.1533083050284441</v>
       </c>
       <c r="C57">
-        <v>-2984.700062416501</v>
+        <v>-3131.108593241701</v>
       </c>
       <c r="D57">
-        <v>2650.289937583499</v>
+        <v>2612.079406758299</v>
       </c>
       <c r="E57">
-        <v>1962.690000000001</v>
+        <v>2070.888</v>
       </c>
       <c r="F57">
-        <v>5950.89</v>
+        <v>6059.088</v>
       </c>
       <c r="G57">
         <v>315.9</v>
@@ -5955,37 +5955,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M57">
-        <v>1194.938712</v>
+        <v>1216.6648704</v>
       </c>
       <c r="N57">
-        <v>-833.4720453333334</v>
+        <v>-855.1982037333332</v>
       </c>
       <c r="O57">
-        <v>-233.3721726933334</v>
+        <v>-239.4554970453333</v>
       </c>
       <c r="P57">
-        <v>-600.0998726400001</v>
+        <v>-615.7427066879999</v>
       </c>
       <c r="Q57">
-        <v>-154.8998726400001</v>
+        <v>-170.5427066879999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1126055859347216</v>
+        <v>0.1141238947059653</v>
       </c>
       <c r="T57">
-        <v>1.542854178630985</v>
+        <v>1.577919046327144</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08469946253332757</v>
+        <v>0.08318697213094671</v>
       </c>
       <c r="W57">
-        <v>0.1837923479233078</v>
+        <v>0.1840960559961059</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3024980804761698</v>
+        <v>0.2970963290390953</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1533083050284441</v>
+        <v>0.1548583050284441</v>
       </c>
       <c r="C58">
-        <v>-3131.108593241701</v>
+        <v>-3276.430983533843</v>
       </c>
       <c r="D58">
-        <v>2612.079406758299</v>
+        <v>2574.955016466157</v>
       </c>
       <c r="E58">
-        <v>2070.888</v>
+        <v>2179.086</v>
       </c>
       <c r="F58">
-        <v>6059.088</v>
+        <v>6167.286</v>
       </c>
       <c r="G58">
         <v>315.9</v>
@@ -6037,37 +6037,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M58">
-        <v>1216.6648704</v>
+        <v>1238.3910288</v>
       </c>
       <c r="N58">
-        <v>-855.1982037333332</v>
+        <v>-876.9243621333333</v>
       </c>
       <c r="O58">
-        <v>-239.4554970453333</v>
+        <v>-245.5388213973334</v>
       </c>
       <c r="P58">
-        <v>-615.7427066879999</v>
+        <v>-631.3855407359999</v>
       </c>
       <c r="Q58">
-        <v>-170.5427066879999</v>
+        <v>-186.185540736</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1141238947059653</v>
+        <v>0.115712822489825</v>
       </c>
       <c r="T58">
-        <v>1.577919046327144</v>
+        <v>1.614614838102194</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08318697213094671</v>
+        <v>0.0817275515672459</v>
       </c>
       <c r="W58">
-        <v>0.1840960559961059</v>
+        <v>0.184389107645297</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2970963290390953</v>
+        <v>0.2918841127401639</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1548583050284441</v>
+        <v>0.1564083050284441</v>
       </c>
       <c r="C59">
-        <v>-3276.430983533843</v>
+        <v>-3420.71289490466</v>
       </c>
       <c r="D59">
-        <v>2574.955016466157</v>
+        <v>2538.87110509534</v>
       </c>
       <c r="E59">
-        <v>2179.086</v>
+        <v>2287.284000000001</v>
       </c>
       <c r="F59">
-        <v>6167.286</v>
+        <v>6275.484</v>
       </c>
       <c r="G59">
         <v>315.9</v>
@@ -6119,37 +6119,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M59">
-        <v>1238.3910288</v>
+        <v>1260.1171872</v>
       </c>
       <c r="N59">
-        <v>-876.9243621333333</v>
+        <v>-898.6505205333335</v>
       </c>
       <c r="O59">
-        <v>-245.5388213973334</v>
+        <v>-251.6221457493334</v>
       </c>
       <c r="P59">
-        <v>-631.3855407359999</v>
+        <v>-647.0283747840001</v>
       </c>
       <c r="Q59">
-        <v>-186.185540736</v>
+        <v>-201.8283747840001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.115712822489825</v>
+        <v>0.1173774135014875</v>
       </c>
       <c r="T59">
-        <v>1.614614838102194</v>
+        <v>1.653058048533198</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.0817275515672459</v>
+        <v>0.08031845585056922</v>
       </c>
       <c r="W59">
-        <v>0.184389107645297</v>
+        <v>0.1846720540652057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2918841127401639</v>
+        <v>0.2868516280377472</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1564083050284441</v>
+        <v>0.157958305028444</v>
       </c>
       <c r="C60">
-        <v>-3420.712894904658</v>
+        <v>-3563.997464837216</v>
       </c>
       <c r="D60">
-        <v>2538.871105095341</v>
+        <v>2503.784535162783</v>
       </c>
       <c r="E60">
-        <v>2287.284</v>
+        <v>2395.481999999999</v>
       </c>
       <c r="F60">
-        <v>6275.483999999999</v>
+        <v>6383.681999999999</v>
       </c>
       <c r="G60">
         <v>315.9</v>
@@ -6201,37 +6201,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M60">
-        <v>1260.1171872</v>
+        <v>1281.8433456</v>
       </c>
       <c r="N60">
-        <v>-898.6505205333333</v>
+        <v>-920.3766789333331</v>
       </c>
       <c r="O60">
-        <v>-251.6221457493334</v>
+        <v>-257.7054701013333</v>
       </c>
       <c r="P60">
-        <v>-647.0283747839999</v>
+        <v>-662.6712088319998</v>
       </c>
       <c r="Q60">
-        <v>-201.8283747839999</v>
+        <v>-217.4712088319998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1173774135014875</v>
+        <v>0.1191232040746945</v>
       </c>
       <c r="T60">
-        <v>1.653058048533198</v>
+        <v>1.693376537521812</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.08031845585056925</v>
+        <v>0.07895712609039011</v>
       </c>
       <c r="W60">
-        <v>0.1846720540652057</v>
+        <v>0.1849454090810497</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2868516280377472</v>
+        <v>0.2819897360371075</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.157958305028444</v>
+        <v>0.159508305028444</v>
       </c>
       <c r="C61">
-        <v>-3563.997464837216</v>
+        <v>-3706.325478722583</v>
       </c>
       <c r="D61">
-        <v>2503.784535162783</v>
+        <v>2469.654521277416</v>
       </c>
       <c r="E61">
-        <v>2395.481999999999</v>
+        <v>2503.679999999999</v>
       </c>
       <c r="F61">
-        <v>6383.681999999999</v>
+        <v>6491.879999999999</v>
       </c>
       <c r="G61">
         <v>315.9</v>
@@ -6283,37 +6283,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M61">
-        <v>1281.8433456</v>
+        <v>1303.569504</v>
       </c>
       <c r="N61">
-        <v>-920.3766789333331</v>
+        <v>-942.1028373333331</v>
       </c>
       <c r="O61">
-        <v>-257.7054701013333</v>
+        <v>-263.7887944533333</v>
       </c>
       <c r="P61">
-        <v>-662.6712088319998</v>
+        <v>-678.3140428799998</v>
       </c>
       <c r="Q61">
-        <v>-217.4712088319998</v>
+        <v>-233.1140428799998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1191232040746945</v>
+        <v>0.1209562841765618</v>
       </c>
       <c r="T61">
-        <v>1.693376537521812</v>
+        <v>1.735710950959858</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07895712609039011</v>
+        <v>0.07764117398888362</v>
       </c>
       <c r="W61">
-        <v>0.1849454090810497</v>
+        <v>0.1852096522630322</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2819897360371075</v>
+        <v>0.2772899071031557</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.159508305028444</v>
+        <v>0.161058305028444</v>
       </c>
       <c r="C62">
-        <v>-3706.325478722583</v>
+        <v>-3847.73552801513</v>
       </c>
       <c r="D62">
-        <v>2469.654521277416</v>
+        <v>2436.44247198487</v>
       </c>
       <c r="E62">
-        <v>2503.679999999999</v>
+        <v>2611.878</v>
       </c>
       <c r="F62">
-        <v>6491.879999999999</v>
+        <v>6600.078</v>
       </c>
       <c r="G62">
         <v>315.9</v>
@@ -6365,37 +6365,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M62">
-        <v>1303.569504</v>
+        <v>1325.2956624</v>
       </c>
       <c r="N62">
-        <v>-942.1028373333331</v>
+        <v>-963.8289957333332</v>
       </c>
       <c r="O62">
-        <v>-263.7887944533333</v>
+        <v>-269.8721188053333</v>
       </c>
       <c r="P62">
-        <v>-678.3140428799998</v>
+        <v>-693.9568769279999</v>
       </c>
       <c r="Q62">
-        <v>-233.1140428799998</v>
+        <v>-248.7568769279999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1209562841765618</v>
+        <v>0.1228833683862173</v>
       </c>
       <c r="T62">
-        <v>1.735710950959858</v>
+        <v>1.780216359958829</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07764117398888362</v>
+        <v>0.07636836785791831</v>
       </c>
       <c r="W62">
-        <v>0.1852096522630322</v>
+        <v>0.18546523173413</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2772899071031557</v>
+        <v>0.2727441709211368</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.161058305028444</v>
+        <v>0.162608305028444</v>
       </c>
       <c r="C63">
-        <v>-3847.73552801513</v>
+        <v>-3988.264155795894</v>
       </c>
       <c r="D63">
-        <v>2436.44247198487</v>
+        <v>2404.111844204106</v>
       </c>
       <c r="E63">
-        <v>2611.878</v>
+        <v>2720.076</v>
       </c>
       <c r="F63">
-        <v>6600.078</v>
+        <v>6708.276</v>
       </c>
       <c r="G63">
         <v>315.9</v>
@@ -6447,37 +6447,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M63">
-        <v>1325.2956624</v>
+        <v>1347.0218208</v>
       </c>
       <c r="N63">
-        <v>-963.8289957333332</v>
+        <v>-985.5551541333334</v>
       </c>
       <c r="O63">
-        <v>-269.8721188053333</v>
+        <v>-275.9554431573334</v>
       </c>
       <c r="P63">
-        <v>-693.9568769279999</v>
+        <v>-709.5997109760001</v>
       </c>
       <c r="Q63">
-        <v>-248.7568769279999</v>
+        <v>-264.3997109760001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1228833683862173</v>
+        <v>0.1249118780805914</v>
       </c>
       <c r="T63">
-        <v>1.780216359958829</v>
+        <v>1.827064158905114</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.07636836785791831</v>
+        <v>0.0751366199892422</v>
       </c>
       <c r="W63">
-        <v>0.18546523173413</v>
+        <v>0.1857125667061602</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2727441709211368</v>
+        <v>0.2683450713901506</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.162608305028444</v>
+        <v>0.1641583050284441</v>
       </c>
       <c r="C64">
-        <v>-3988.264155795894</v>
+        <v>-4127.945990898304</v>
       </c>
       <c r="D64">
-        <v>2404.111844204106</v>
+        <v>2372.628009101695</v>
       </c>
       <c r="E64">
-        <v>2720.076</v>
+        <v>2828.273999999999</v>
       </c>
       <c r="F64">
-        <v>6708.276</v>
+        <v>6816.473999999999</v>
       </c>
       <c r="G64">
         <v>315.9</v>
@@ -6529,37 +6529,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M64">
-        <v>1347.0218208</v>
+        <v>1368.7479792</v>
       </c>
       <c r="N64">
-        <v>-985.5551541333334</v>
+        <v>-1007.281312533333</v>
       </c>
       <c r="O64">
-        <v>-275.9554431573334</v>
+        <v>-282.0387675093334</v>
       </c>
       <c r="P64">
-        <v>-709.5997109760001</v>
+        <v>-725.2425450239998</v>
       </c>
       <c r="Q64">
-        <v>-264.3997109760001</v>
+        <v>-280.0425450239998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1249118780805914</v>
+        <v>0.1270500369476344</v>
       </c>
       <c r="T64">
-        <v>1.827064158905114</v>
+        <v>1.876444271307955</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.0751366199892422</v>
+        <v>0.0739439752275082</v>
       </c>
       <c r="W64">
-        <v>0.1857125667061602</v>
+        <v>0.1859520497743164</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2683450713901506</v>
+        <v>0.2640856258125293</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1641583050284441</v>
+        <v>0.165708305028444</v>
       </c>
       <c r="C65">
-        <v>-4127.945990898304</v>
+        <v>-4266.813871631213</v>
       </c>
       <c r="D65">
-        <v>2372.628009101695</v>
+        <v>2341.958128368787</v>
       </c>
       <c r="E65">
-        <v>2828.273999999999</v>
+        <v>2936.472</v>
       </c>
       <c r="F65">
-        <v>6816.473999999999</v>
+        <v>6924.672</v>
       </c>
       <c r="G65">
         <v>315.9</v>
@@ -6611,37 +6611,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M65">
-        <v>1368.7479792</v>
+        <v>1390.4741376</v>
       </c>
       <c r="N65">
-        <v>-1007.281312533333</v>
+        <v>-1029.007470933333</v>
       </c>
       <c r="O65">
-        <v>-282.0387675093334</v>
+        <v>-288.1220918613333</v>
       </c>
       <c r="P65">
-        <v>-725.2425450239998</v>
+        <v>-740.885379072</v>
       </c>
       <c r="Q65">
-        <v>-280.0425450239998</v>
+        <v>-295.685379072</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1270500369476344</v>
+        <v>0.129306982418402</v>
       </c>
       <c r="T65">
-        <v>1.876444271307955</v>
+        <v>1.928567723288731</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0739439752275082</v>
+        <v>0.07278860061457838</v>
       </c>
       <c r="W65">
-        <v>0.1859520497743164</v>
+        <v>0.1861840489965927</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2640856258125293</v>
+        <v>0.2599592879092084</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.165708305028444</v>
+        <v>0.167258305028444</v>
       </c>
       <c r="C66">
-        <v>-4266.813871631213</v>
+        <v>-4404.898960028516</v>
       </c>
       <c r="D66">
-        <v>2341.958128368787</v>
+        <v>2312.071039971484</v>
       </c>
       <c r="E66">
-        <v>2936.472</v>
+        <v>3044.67</v>
       </c>
       <c r="F66">
-        <v>6924.672</v>
+        <v>7032.87</v>
       </c>
       <c r="G66">
         <v>315.9</v>
@@ -6693,37 +6693,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M66">
-        <v>1390.4741376</v>
+        <v>1412.200296</v>
       </c>
       <c r="N66">
-        <v>-1029.007470933333</v>
+        <v>-1050.733629333333</v>
       </c>
       <c r="O66">
-        <v>-288.1220918613333</v>
+        <v>-294.2054162133334</v>
       </c>
       <c r="P66">
-        <v>-740.885379072</v>
+        <v>-756.5282131199999</v>
       </c>
       <c r="Q66">
-        <v>-295.685379072</v>
+        <v>-311.3282131199999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.129306982418402</v>
+        <v>0.131692896201785</v>
       </c>
       <c r="T66">
-        <v>1.928567723288731</v>
+        <v>1.983669658239838</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.07278860061457838</v>
+        <v>0.0716687759897387</v>
       </c>
       <c r="W66">
-        <v>0.1861840489965927</v>
+        <v>0.1864089097812605</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2599592879092084</v>
+        <v>0.2559599142490667</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.167258305028444</v>
+        <v>0.168808305028444</v>
       </c>
       <c r="C67">
-        <v>-4404.898960028516</v>
+        <v>-4542.230847460971</v>
       </c>
       <c r="D67">
-        <v>2312.071039971484</v>
+        <v>2282.937152539029</v>
       </c>
       <c r="E67">
-        <v>3044.67</v>
+        <v>3152.868</v>
       </c>
       <c r="F67">
-        <v>7032.87</v>
+        <v>7141.068</v>
       </c>
       <c r="G67">
         <v>315.9</v>
@@ -6775,37 +6775,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M67">
-        <v>1412.200296</v>
+        <v>1433.9264544</v>
       </c>
       <c r="N67">
-        <v>-1050.733629333333</v>
+        <v>-1072.459787733333</v>
       </c>
       <c r="O67">
-        <v>-294.2054162133334</v>
+        <v>-300.2887405653333</v>
       </c>
       <c r="P67">
-        <v>-756.5282131199999</v>
+        <v>-772.171047168</v>
       </c>
       <c r="Q67">
-        <v>-311.3282131199999</v>
+        <v>-326.971047168</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.131692896201785</v>
+        <v>0.1342191578547786</v>
       </c>
       <c r="T67">
-        <v>1.983669658239838</v>
+        <v>2.042012883482186</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0716687759897387</v>
+        <v>0.07058288544443964</v>
       </c>
       <c r="W67">
-        <v>0.1864089097812605</v>
+        <v>0.1866269566027565</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2559599142490667</v>
+        <v>0.2520817337301415</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.168808305028444</v>
+        <v>0.1703583050284441</v>
       </c>
       <c r="C68">
-        <v>-4542.230847460971</v>
+        <v>-4678.837652362639</v>
       </c>
       <c r="D68">
-        <v>2282.937152539029</v>
+        <v>2254.52834763736</v>
       </c>
       <c r="E68">
-        <v>3152.868</v>
+        <v>3261.066</v>
       </c>
       <c r="F68">
-        <v>7141.068</v>
+        <v>7249.266</v>
       </c>
       <c r="G68">
         <v>315.9</v>
@@ -6857,37 +6857,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M68">
-        <v>1433.9264544</v>
+        <v>1455.6526128</v>
       </c>
       <c r="N68">
-        <v>-1072.459787733333</v>
+        <v>-1094.185946133333</v>
       </c>
       <c r="O68">
-        <v>-300.2887405653333</v>
+        <v>-306.3720649173334</v>
       </c>
       <c r="P68">
-        <v>-772.171047168</v>
+        <v>-787.813881216</v>
       </c>
       <c r="Q68">
-        <v>-326.971047168</v>
+        <v>-342.613881216</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1342191578547786</v>
+        <v>0.1368985262746204</v>
       </c>
       <c r="T68">
-        <v>2.042012883482186</v>
+        <v>2.103892061769525</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07058288544443964</v>
+        <v>0.06952940954228382</v>
       </c>
       <c r="W68">
-        <v>0.1866269566027565</v>
+        <v>0.1868384945639094</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2520817337301415</v>
+        <v>0.2483193197938708</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1703583050284441</v>
+        <v>0.1719083050284441</v>
       </c>
       <c r="C69">
-        <v>-4678.837652362639</v>
+        <v>-4814.74611075037</v>
       </c>
       <c r="D69">
-        <v>2254.52834763736</v>
+        <v>2226.81788924963</v>
       </c>
       <c r="E69">
-        <v>3261.066</v>
+        <v>3369.264</v>
       </c>
       <c r="F69">
-        <v>7249.266</v>
+        <v>7357.464</v>
       </c>
       <c r="G69">
         <v>315.9</v>
@@ -6939,37 +6939,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M69">
-        <v>1455.6526128</v>
+        <v>1477.3787712</v>
       </c>
       <c r="N69">
-        <v>-1094.185946133333</v>
+        <v>-1115.912104533333</v>
       </c>
       <c r="O69">
-        <v>-306.3720649173334</v>
+        <v>-312.4553892693334</v>
       </c>
       <c r="P69">
-        <v>-787.813881216</v>
+        <v>-803.456715264</v>
       </c>
       <c r="Q69">
-        <v>-342.613881216</v>
+        <v>-358.256715264</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1368985262746204</v>
+        <v>0.1397453552207023</v>
       </c>
       <c r="T69">
-        <v>2.103892061769525</v>
+        <v>2.169638688699823</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.06952940954228382</v>
+        <v>0.06850691822548553</v>
       </c>
       <c r="W69">
-        <v>0.1868384945639094</v>
+        <v>0.1870438108203225</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2483193197938708</v>
+        <v>0.2446675650910197</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1719083050284441</v>
+        <v>0.1734583050284441</v>
       </c>
       <c r="C70">
-        <v>-4814.74611075037</v>
+        <v>-4949.981660148882</v>
       </c>
       <c r="D70">
-        <v>2226.81788924963</v>
+        <v>2199.780339851118</v>
       </c>
       <c r="E70">
-        <v>3369.264</v>
+        <v>3477.462</v>
       </c>
       <c r="F70">
-        <v>7357.464</v>
+        <v>7465.662</v>
       </c>
       <c r="G70">
         <v>315.9</v>
@@ -7021,37 +7021,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M70">
-        <v>1477.3787712</v>
+        <v>1499.1049296</v>
       </c>
       <c r="N70">
-        <v>-1115.912104533333</v>
+        <v>-1137.638262933333</v>
       </c>
       <c r="O70">
-        <v>-312.4553892693334</v>
+        <v>-318.5387136213334</v>
       </c>
       <c r="P70">
-        <v>-803.456715264</v>
+        <v>-819.099549312</v>
       </c>
       <c r="Q70">
-        <v>-358.256715264</v>
+        <v>-373.899549312</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1397453552207023</v>
+        <v>0.1427758505504024</v>
       </c>
       <c r="T70">
-        <v>2.169638688699823</v>
+        <v>2.239627033496591</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.06850691822548553</v>
+        <v>0.06751406433815965</v>
       </c>
       <c r="W70">
-        <v>0.1870438108203225</v>
+        <v>0.1872431758808976</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2446675650910197</v>
+        <v>0.2411216583505701</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1734583050284441</v>
+        <v>0.1750083050284441</v>
       </c>
       <c r="C71">
-        <v>-4949.981660148882</v>
+        <v>-5084.568517475187</v>
       </c>
       <c r="D71">
-        <v>2199.780339851118</v>
+        <v>2173.391482524813</v>
       </c>
       <c r="E71">
-        <v>3477.462</v>
+        <v>3585.660000000001</v>
       </c>
       <c r="F71">
-        <v>7465.662</v>
+        <v>7573.860000000001</v>
       </c>
       <c r="G71">
         <v>315.9</v>
@@ -7103,37 +7103,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M71">
-        <v>1499.1049296</v>
+        <v>1520.831088</v>
       </c>
       <c r="N71">
-        <v>-1137.638262933333</v>
+        <v>-1159.364421333333</v>
       </c>
       <c r="O71">
-        <v>-318.5387136213334</v>
+        <v>-324.6220379733334</v>
       </c>
       <c r="P71">
-        <v>-819.099549312</v>
+        <v>-834.7423833600001</v>
       </c>
       <c r="Q71">
-        <v>-373.899549312</v>
+        <v>-389.5423833600001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1427758505504024</v>
+        <v>0.1460083789020825</v>
       </c>
       <c r="T71">
-        <v>2.239627033496591</v>
+        <v>2.314281267946478</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.06751406433815965</v>
+        <v>0.06654957770475738</v>
       </c>
       <c r="W71">
-        <v>0.1872431758808976</v>
+        <v>0.1874368447968847</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2411216583505701</v>
+        <v>0.2376770632312762</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1750083050284441</v>
+        <v>0.1765583050284441</v>
       </c>
       <c r="C72">
-        <v>-5084.568517475187</v>
+        <v>-5218.529751383585</v>
       </c>
       <c r="D72">
-        <v>2173.391482524813</v>
+        <v>2147.628248616415</v>
       </c>
       <c r="E72">
-        <v>3585.660000000001</v>
+        <v>3693.858</v>
       </c>
       <c r="F72">
-        <v>7573.860000000001</v>
+        <v>7682.058</v>
       </c>
       <c r="G72">
         <v>315.9</v>
@@ -7185,37 +7185,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M72">
-        <v>1520.831088</v>
+        <v>1542.5572464</v>
       </c>
       <c r="N72">
-        <v>-1159.364421333333</v>
+        <v>-1181.090579733333</v>
       </c>
       <c r="O72">
-        <v>-324.6220379733334</v>
+        <v>-330.7053623253333</v>
       </c>
       <c r="P72">
-        <v>-834.7423833600001</v>
+        <v>-850.3852174079999</v>
       </c>
       <c r="Q72">
-        <v>-389.5423833600001</v>
+        <v>-405.1852174079999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1460083789020825</v>
+        <v>0.1494638402435336</v>
       </c>
       <c r="T72">
-        <v>2.314281267946478</v>
+        <v>2.39408407028946</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.06654957770475738</v>
+        <v>0.06561225970891572</v>
       </c>
       <c r="W72">
-        <v>0.1874368447968847</v>
+        <v>0.1876250582504497</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2376770632312762</v>
+        <v>0.2343294989604132</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1765583050284441</v>
+        <v>0.178108305028444</v>
       </c>
       <c r="C73">
-        <v>-5218.529751383583</v>
+        <v>-5351.887349525512</v>
       </c>
       <c r="D73">
-        <v>2147.628248616415</v>
+        <v>2122.468650474487</v>
       </c>
       <c r="E73">
-        <v>3693.857999999999</v>
+        <v>3802.056</v>
       </c>
       <c r="F73">
-        <v>7682.057999999999</v>
+        <v>7790.255999999999</v>
       </c>
       <c r="G73">
         <v>315.9</v>
@@ -7267,37 +7267,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M73">
-        <v>1542.5572464</v>
+        <v>1564.2834048</v>
       </c>
       <c r="N73">
-        <v>-1181.090579733333</v>
+        <v>-1202.816738133333</v>
       </c>
       <c r="O73">
-        <v>-330.7053623253333</v>
+        <v>-336.7886866773334</v>
       </c>
       <c r="P73">
-        <v>-850.3852174079999</v>
+        <v>-866.028051456</v>
       </c>
       <c r="Q73">
-        <v>-405.1852174079999</v>
+        <v>-420.828051456</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1494638402435336</v>
+        <v>0.1531661202522312</v>
       </c>
       <c r="T73">
-        <v>2.394084070289459</v>
+        <v>2.479587072799797</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.06561225970891572</v>
+        <v>0.06470097832406968</v>
       </c>
       <c r="W73">
-        <v>0.1876250582504497</v>
+        <v>0.1878080435525268</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2343294989604132</v>
+        <v>0.2310749225859631</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.178108305028444</v>
+        <v>0.179658305028444</v>
       </c>
       <c r="C74">
-        <v>-5351.887349525512</v>
+        <v>-5484.662281136416</v>
       </c>
       <c r="D74">
-        <v>2122.468650474487</v>
+        <v>2097.891718863583</v>
       </c>
       <c r="E74">
-        <v>3802.056</v>
+        <v>3910.254</v>
       </c>
       <c r="F74">
-        <v>7790.255999999999</v>
+        <v>7898.454</v>
       </c>
       <c r="G74">
         <v>315.9</v>
@@ -7349,37 +7349,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M74">
-        <v>1564.2834048</v>
+        <v>1586.0095632</v>
       </c>
       <c r="N74">
-        <v>-1202.816738133333</v>
+        <v>-1224.542896533333</v>
       </c>
       <c r="O74">
-        <v>-336.7886866773334</v>
+        <v>-342.8720110293334</v>
       </c>
       <c r="P74">
-        <v>-866.028051456</v>
+        <v>-881.6708855039999</v>
       </c>
       <c r="Q74">
-        <v>-420.828051456</v>
+        <v>-436.4708855039999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1531661202522312</v>
+        <v>0.1571426432245361</v>
       </c>
       <c r="T74">
-        <v>2.479587072799797</v>
+        <v>2.571423631051641</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.06470097832406968</v>
+        <v>0.06381466355250708</v>
       </c>
       <c r="W74">
-        <v>0.1878080435525268</v>
+        <v>0.1879860155586566</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2310749225859631</v>
+        <v>0.2279095126875252</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.179658305028444</v>
+        <v>0.181208305028444</v>
       </c>
       <c r="C75">
-        <v>-5484.662281136416</v>
+        <v>-5616.87455532407</v>
       </c>
       <c r="D75">
-        <v>2097.891718863583</v>
+        <v>2073.87744467593</v>
       </c>
       <c r="E75">
-        <v>3910.254</v>
+        <v>4018.451999999999</v>
       </c>
       <c r="F75">
-        <v>7898.454</v>
+        <v>8006.651999999999</v>
       </c>
       <c r="G75">
         <v>315.9</v>
@@ -7431,37 +7431,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M75">
-        <v>1586.0095632</v>
+        <v>1607.7357216</v>
       </c>
       <c r="N75">
-        <v>-1224.542896533333</v>
+        <v>-1246.269054933333</v>
       </c>
       <c r="O75">
-        <v>-342.8720110293334</v>
+        <v>-348.9553353813333</v>
       </c>
       <c r="P75">
-        <v>-881.6708855039999</v>
+        <v>-897.3137195519998</v>
       </c>
       <c r="Q75">
-        <v>-436.4708855039999</v>
+        <v>-452.1137195519998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1571426432245361</v>
+        <v>0.1614250525793259</v>
       </c>
       <c r="T75">
-        <v>2.571423631051641</v>
+        <v>2.670324539938242</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.06381466355250708</v>
+        <v>0.06295230323422996</v>
       </c>
       <c r="W75">
-        <v>0.1879860155586566</v>
+        <v>0.1881591775105666</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2279095126875252</v>
+        <v>0.2248296544079641</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.181208305028444</v>
+        <v>0.1827583050284441</v>
       </c>
       <c r="C76">
-        <v>-5616.87455532407</v>
+        <v>-5748.543275398914</v>
       </c>
       <c r="D76">
-        <v>2073.87744467593</v>
+        <v>2050.406724601085</v>
       </c>
       <c r="E76">
-        <v>4018.451999999999</v>
+        <v>4126.65</v>
       </c>
       <c r="F76">
-        <v>8006.651999999999</v>
+        <v>8114.849999999999</v>
       </c>
       <c r="G76">
         <v>315.9</v>
@@ -7513,37 +7513,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M76">
-        <v>1607.7357216</v>
+        <v>1629.46188</v>
       </c>
       <c r="N76">
-        <v>-1246.269054933333</v>
+        <v>-1267.995213333333</v>
       </c>
       <c r="O76">
-        <v>-348.9553353813333</v>
+        <v>-355.0386597333333</v>
       </c>
       <c r="P76">
-        <v>-897.3137195519998</v>
+        <v>-912.9565535999998</v>
       </c>
       <c r="Q76">
-        <v>-452.1137195519998</v>
+        <v>-467.7565535999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1614250525793259</v>
+        <v>0.166050054682499</v>
       </c>
       <c r="T76">
-        <v>2.670324539938242</v>
+        <v>2.777137521535773</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.06295230323422996</v>
+        <v>0.06211293919110689</v>
       </c>
       <c r="W76">
-        <v>0.1881591775105666</v>
+        <v>0.1883277218104258</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2248296544079641</v>
+        <v>0.2218319256825245</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1827583050284441</v>
+        <v>0.1843083050284441</v>
       </c>
       <c r="C77">
-        <v>-5748.543275398914</v>
+        <v>-5879.686689556418</v>
       </c>
       <c r="D77">
-        <v>2050.406724601085</v>
+        <v>2027.461310443581</v>
       </c>
       <c r="E77">
-        <v>4126.65</v>
+        <v>4234.847999999999</v>
       </c>
       <c r="F77">
-        <v>8114.849999999999</v>
+        <v>8223.047999999999</v>
       </c>
       <c r="G77">
         <v>315.9</v>
@@ -7595,37 +7595,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M77">
-        <v>1629.46188</v>
+        <v>1651.1880384</v>
       </c>
       <c r="N77">
-        <v>-1267.995213333333</v>
+        <v>-1289.721371733333</v>
       </c>
       <c r="O77">
-        <v>-355.0386597333333</v>
+        <v>-361.1219840853333</v>
       </c>
       <c r="P77">
-        <v>-912.9565535999998</v>
+        <v>-928.5993876479998</v>
       </c>
       <c r="Q77">
-        <v>-467.7565535999998</v>
+        <v>-483.3993876479998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.166050054682499</v>
+        <v>0.1710604736276031</v>
       </c>
       <c r="T77">
-        <v>2.777137521535773</v>
+        <v>2.892851584933097</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.06211293919110689</v>
+        <v>0.06129566367543442</v>
       </c>
       <c r="W77">
-        <v>0.1883277218104258</v>
+        <v>0.1884918307339728</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2218319256825245</v>
+        <v>0.2189130845551229</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1843083050284441</v>
+        <v>0.185858305028444</v>
       </c>
       <c r="C78">
-        <v>-5879.686689556418</v>
+        <v>-6010.322238194105</v>
       </c>
       <c r="D78">
-        <v>2027.461310443581</v>
+        <v>2005.023761805895</v>
       </c>
       <c r="E78">
-        <v>4234.847999999999</v>
+        <v>4343.045999999999</v>
       </c>
       <c r="F78">
-        <v>8223.047999999999</v>
+        <v>8331.245999999999</v>
       </c>
       <c r="G78">
         <v>315.9</v>
@@ -7677,37 +7677,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M78">
-        <v>1651.1880384</v>
+        <v>1672.9141968</v>
       </c>
       <c r="N78">
-        <v>-1289.721371733333</v>
+        <v>-1311.447530133333</v>
       </c>
       <c r="O78">
-        <v>-361.1219840853333</v>
+        <v>-367.2053084373333</v>
       </c>
       <c r="P78">
-        <v>-928.5993876479998</v>
+        <v>-944.2422216959999</v>
       </c>
       <c r="Q78">
-        <v>-483.3993876479998</v>
+        <v>-499.0422216959999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1710604736276031</v>
+        <v>0.1765065811766293</v>
       </c>
       <c r="T78">
-        <v>2.892851584933097</v>
+        <v>3.018627740799753</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.06129566367543442</v>
+        <v>0.06049961609523398</v>
       </c>
       <c r="W78">
-        <v>0.1884918307339728</v>
+        <v>0.188651677088077</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2189130845551229</v>
+        <v>0.2160700574829785</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.185858305028444</v>
+        <v>0.187408305028444</v>
       </c>
       <c r="C79">
-        <v>-6010.322238194105</v>
+        <v>-6140.466598121052</v>
       </c>
       <c r="D79">
-        <v>2005.023761805895</v>
+        <v>1983.077401878948</v>
       </c>
       <c r="E79">
-        <v>4343.045999999999</v>
+        <v>4451.244</v>
       </c>
       <c r="F79">
-        <v>8331.245999999999</v>
+        <v>8439.444</v>
       </c>
       <c r="G79">
         <v>315.9</v>
@@ -7759,37 +7759,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M79">
-        <v>1672.9141968</v>
+        <v>1694.6403552</v>
       </c>
       <c r="N79">
-        <v>-1311.447530133333</v>
+        <v>-1333.173688533333</v>
       </c>
       <c r="O79">
-        <v>-367.2053084373333</v>
+        <v>-373.2886327893333</v>
       </c>
       <c r="P79">
-        <v>-944.2422216959999</v>
+        <v>-959.8850557439998</v>
       </c>
       <c r="Q79">
-        <v>-499.0422216959999</v>
+        <v>-514.6850557439998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1765065811766293</v>
+        <v>0.1824477894119307</v>
       </c>
       <c r="T79">
-        <v>3.018627740799753</v>
+        <v>3.155838092654287</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.06049961609523398</v>
+        <v>0.05972397999144893</v>
       </c>
       <c r="W79">
-        <v>0.188651677088077</v>
+        <v>0.1888074248177171</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2160700574829785</v>
+        <v>0.213299928540889</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.187408305028444</v>
+        <v>0.1889583050284441</v>
       </c>
       <c r="C80">
-        <v>-6140.466598121052</v>
+        <v>-6270.13572389543</v>
       </c>
       <c r="D80">
-        <v>1983.077401878948</v>
+        <v>1961.60627610457</v>
       </c>
       <c r="E80">
-        <v>4451.244</v>
+        <v>4559.442</v>
       </c>
       <c r="F80">
-        <v>8439.444</v>
+        <v>8547.642</v>
       </c>
       <c r="G80">
         <v>315.9</v>
@@ -7841,37 +7841,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M80">
-        <v>1694.6403552</v>
+        <v>1716.3665136</v>
       </c>
       <c r="N80">
-        <v>-1333.173688533333</v>
+        <v>-1354.899846933333</v>
       </c>
       <c r="O80">
-        <v>-373.2886327893333</v>
+        <v>-379.3719571413333</v>
       </c>
       <c r="P80">
-        <v>-959.8850557439998</v>
+        <v>-975.527889792</v>
       </c>
       <c r="Q80">
-        <v>-514.6850557439998</v>
+        <v>-530.327889792</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1824477894119307</v>
+        <v>0.188954827002975</v>
       </c>
       <c r="T80">
-        <v>3.155838092654287</v>
+        <v>3.306116097066397</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05972397999144893</v>
+        <v>0.05896798024472173</v>
       </c>
       <c r="W80">
-        <v>0.1888074248177171</v>
+        <v>0.1889592295668599</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.213299928540889</v>
+        <v>0.2105999294454347</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1889583050284441</v>
+        <v>0.190508305028444</v>
       </c>
       <c r="C81">
-        <v>-6270.13572389543</v>
+        <v>-6399.344886505374</v>
       </c>
       <c r="D81">
-        <v>1961.60627610457</v>
+        <v>1940.595113494626</v>
       </c>
       <c r="E81">
-        <v>4559.442</v>
+        <v>4667.64</v>
       </c>
       <c r="F81">
-        <v>8547.642</v>
+        <v>8655.84</v>
       </c>
       <c r="G81">
         <v>315.9</v>
@@ -7923,37 +7923,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M81">
-        <v>1716.3665136</v>
+        <v>1738.092672</v>
       </c>
       <c r="N81">
-        <v>-1354.899846933333</v>
+        <v>-1376.626005333333</v>
       </c>
       <c r="O81">
-        <v>-379.3719571413333</v>
+        <v>-385.4552814933334</v>
       </c>
       <c r="P81">
-        <v>-975.527889792</v>
+        <v>-991.1707238399999</v>
       </c>
       <c r="Q81">
-        <v>-530.327889792</v>
+        <v>-545.9707238399999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.188954827002975</v>
+        <v>0.1961125683531237</v>
       </c>
       <c r="T81">
-        <v>3.306116097066397</v>
+        <v>3.471421901919717</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05896798024472173</v>
+        <v>0.0582308804916627</v>
       </c>
       <c r="W81">
-        <v>0.1889592295668599</v>
+        <v>0.1891072391972741</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2105999294454347</v>
+        <v>0.2079674303273668</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.190508305028444</v>
+        <v>0.1920583050284441</v>
       </c>
       <c r="C82">
-        <v>-6399.344886505374</v>
+        <v>-6528.108709590304</v>
       </c>
       <c r="D82">
-        <v>1940.595113494626</v>
+        <v>1920.029290409696</v>
       </c>
       <c r="E82">
-        <v>4667.64</v>
+        <v>4775.838000000001</v>
       </c>
       <c r="F82">
-        <v>8655.84</v>
+        <v>8764.038</v>
       </c>
       <c r="G82">
         <v>315.9</v>
@@ -8005,37 +8005,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M82">
-        <v>1738.092672</v>
+        <v>1759.8188304</v>
       </c>
       <c r="N82">
-        <v>-1376.626005333333</v>
+        <v>-1398.352163733334</v>
       </c>
       <c r="O82">
-        <v>-385.4552814933334</v>
+        <v>-391.5386058453334</v>
       </c>
       <c r="P82">
-        <v>-991.1707238399999</v>
+        <v>-1006.813557888</v>
       </c>
       <c r="Q82">
-        <v>-545.9707238399999</v>
+        <v>-561.6135578880001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1961125683531237</v>
+        <v>0.2040237561611829</v>
       </c>
       <c r="T82">
-        <v>3.471421901919717</v>
+        <v>3.654128317810228</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0582308804916627</v>
+        <v>0.05751198073250636</v>
       </c>
       <c r="W82">
-        <v>0.1891072391972741</v>
+        <v>0.1892515942689127</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2079674303273668</v>
+        <v>0.2053999311875226</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1920583050284441</v>
+        <v>0.1936083050284441</v>
       </c>
       <c r="C83">
-        <v>-6528.108709590304</v>
+        <v>-6656.44120338321</v>
       </c>
       <c r="D83">
-        <v>1920.029290409696</v>
+        <v>1899.894796616791</v>
       </c>
       <c r="E83">
-        <v>4775.838000000001</v>
+        <v>4884.036000000001</v>
       </c>
       <c r="F83">
-        <v>8764.038</v>
+        <v>8872.236000000001</v>
       </c>
       <c r="G83">
         <v>315.9</v>
@@ -8087,37 +8087,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M83">
-        <v>1759.8188304</v>
+        <v>1781.5449888</v>
       </c>
       <c r="N83">
-        <v>-1398.352163733334</v>
+        <v>-1420.078322133334</v>
       </c>
       <c r="O83">
-        <v>-391.5386058453334</v>
+        <v>-397.6219301973334</v>
       </c>
       <c r="P83">
-        <v>-1006.813557888</v>
+        <v>-1022.456391936</v>
       </c>
       <c r="Q83">
-        <v>-561.6135578880001</v>
+        <v>-577.2563919360002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2040237561611829</v>
+        <v>0.2128139648368041</v>
       </c>
       <c r="T83">
-        <v>3.654128317810228</v>
+        <v>3.857135446577463</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.05751198073250636</v>
+        <v>0.05681061511381726</v>
       </c>
       <c r="W83">
-        <v>0.1892515942689127</v>
+        <v>0.1893924284851455</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2053999311875226</v>
+        <v>0.2028950539779187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1936083050284441</v>
+        <v>0.1951583050284441</v>
       </c>
       <c r="C84">
-        <v>-6656.44120338321</v>
+        <v>-6784.355796539479</v>
       </c>
       <c r="D84">
-        <v>1899.894796616791</v>
+        <v>1880.17820346052</v>
       </c>
       <c r="E84">
-        <v>4884.036000000001</v>
+        <v>4992.233999999999</v>
       </c>
       <c r="F84">
-        <v>8872.236000000001</v>
+        <v>8980.433999999999</v>
       </c>
       <c r="G84">
         <v>315.9</v>
@@ -8169,37 +8169,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M84">
-        <v>1781.5449888</v>
+        <v>1803.2711472</v>
       </c>
       <c r="N84">
-        <v>-1420.078322133334</v>
+        <v>-1441.804480533333</v>
       </c>
       <c r="O84">
-        <v>-397.6219301973334</v>
+        <v>-403.7052545493333</v>
       </c>
       <c r="P84">
-        <v>-1022.456391936</v>
+        <v>-1038.099225984</v>
       </c>
       <c r="Q84">
-        <v>-577.2563919360002</v>
+        <v>-592.8992259839997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2128139648368041</v>
+        <v>0.2226383157095574</v>
       </c>
       <c r="T84">
-        <v>3.857135446577463</v>
+        <v>4.084025766964373</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.05681061511381726</v>
+        <v>0.05612614987148213</v>
       </c>
       <c r="W84">
-        <v>0.1893924284851455</v>
+        <v>0.1895298691058064</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2028950539779187</v>
+        <v>0.2004505352552932</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1951583050284441</v>
+        <v>0.2263263322717906</v>
       </c>
       <c r="C85">
-        <v>-6784.355796539479</v>
+        <v>-7217.168187860389</v>
       </c>
       <c r="D85">
-        <v>1880.17820346052</v>
+        <v>1555.56381213961</v>
       </c>
       <c r="E85">
-        <v>4992.233999999999</v>
+        <v>5100.432</v>
       </c>
       <c r="F85">
-        <v>8980.433999999999</v>
+        <v>9088.632</v>
       </c>
       <c r="G85">
         <v>315.9</v>
@@ -8251,45 +8251,45 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M85">
-        <v>1803.2711472</v>
+        <v>2143.0994256</v>
       </c>
       <c r="N85">
-        <v>-1441.804480533333</v>
+        <v>-1781.632758933333</v>
       </c>
       <c r="O85">
-        <v>-403.7052545493333</v>
+        <v>-498.8571725013334</v>
       </c>
       <c r="P85">
-        <v>-1038.099225984</v>
+        <v>-1282.775586432</v>
       </c>
       <c r="Q85">
-        <v>-592.8992259839997</v>
+        <v>-837.5755864319997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2226383157095574</v>
+        <v>0.2350533807123204</v>
       </c>
       <c r="T85">
-        <v>4.084025766964373</v>
+        <v>4.370747822455436</v>
       </c>
       <c r="U85">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05612614987148213</v>
+        <v>0.04722630478907012</v>
       </c>
       <c r="W85">
-        <v>0.1895298691058064</v>
+        <v>0.2246640373307373</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.2004505352552932</v>
+        <v>0.1686653742466789</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2263263322717906</v>
+        <v>0.2282263322717905</v>
       </c>
       <c r="C86">
-        <v>-7217.168187860389</v>
+        <v>-7341.567638639228</v>
       </c>
       <c r="D86">
-        <v>1555.56381213961</v>
+        <v>1539.362361360772</v>
       </c>
       <c r="E86">
-        <v>5100.432</v>
+        <v>5208.63</v>
       </c>
       <c r="F86">
-        <v>9088.632</v>
+        <v>9196.83</v>
       </c>
       <c r="G86">
         <v>315.9</v>
@@ -8333,37 +8333,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M86">
-        <v>2143.0994256</v>
+        <v>2168.612514</v>
       </c>
       <c r="N86">
-        <v>-1781.632758933333</v>
+        <v>-1807.145847333333</v>
       </c>
       <c r="O86">
-        <v>-498.8571725013334</v>
+        <v>-506.0008372533334</v>
       </c>
       <c r="P86">
-        <v>-1282.775586432</v>
+        <v>-1301.14501008</v>
       </c>
       <c r="Q86">
-        <v>-837.5755864319997</v>
+        <v>-855.9450100799997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2350533807123202</v>
+        <v>0.2476702727598082</v>
       </c>
       <c r="T86">
-        <v>4.370747822455432</v>
+        <v>4.662131010619128</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04722630478907012</v>
+        <v>0.04667070120331636</v>
       </c>
       <c r="W86">
-        <v>0.2246640373307373</v>
+        <v>0.224795048656258</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1686653742466789</v>
+        <v>0.1666810757261298</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2282263322717905</v>
+        <v>0.2301263322717905</v>
       </c>
       <c r="C87">
-        <v>-7341.567638639228</v>
+        <v>-7465.633086607933</v>
       </c>
       <c r="D87">
-        <v>1539.362361360772</v>
+        <v>1523.494913392065</v>
       </c>
       <c r="E87">
-        <v>5208.63</v>
+        <v>5316.827999999999</v>
       </c>
       <c r="F87">
-        <v>9196.83</v>
+        <v>9305.027999999998</v>
       </c>
       <c r="G87">
         <v>315.9</v>
@@ -8415,37 +8415,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M87">
-        <v>2168.612514</v>
+        <v>2194.1256024</v>
       </c>
       <c r="N87">
-        <v>-1807.145847333333</v>
+        <v>-1832.658935733333</v>
       </c>
       <c r="O87">
-        <v>-506.0008372533334</v>
+        <v>-513.1445020053334</v>
       </c>
       <c r="P87">
-        <v>-1301.14501008</v>
+        <v>-1319.514433728</v>
       </c>
       <c r="Q87">
-        <v>-855.9450100799997</v>
+        <v>-874.3144337279998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2476702727598082</v>
+        <v>0.2620895779569374</v>
       </c>
       <c r="T87">
-        <v>4.662131010619128</v>
+        <v>4.995140368520495</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04667070120331636</v>
+        <v>0.04612801863118476</v>
       </c>
       <c r="W87">
-        <v>0.224795048656258</v>
+        <v>0.2249230132067666</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1666810757261298</v>
+        <v>0.1647429236828027</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2301263322717905</v>
+        <v>0.2320263322717906</v>
       </c>
       <c r="C88">
-        <v>-7465.633086607933</v>
+        <v>-7589.374754896588</v>
       </c>
       <c r="D88">
-        <v>1523.494913392065</v>
+        <v>1507.951245103411</v>
       </c>
       <c r="E88">
-        <v>5316.827999999999</v>
+        <v>5425.025999999999</v>
       </c>
       <c r="F88">
-        <v>9305.027999999998</v>
+        <v>9413.225999999999</v>
       </c>
       <c r="G88">
         <v>315.9</v>
@@ -8497,37 +8497,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M88">
-        <v>2194.1256024</v>
+        <v>2219.6386908</v>
       </c>
       <c r="N88">
-        <v>-1832.658935733333</v>
+        <v>-1858.172024133333</v>
       </c>
       <c r="O88">
-        <v>-513.1445020053334</v>
+        <v>-520.2881667573333</v>
       </c>
       <c r="P88">
-        <v>-1319.514433728</v>
+        <v>-1337.883857376</v>
       </c>
       <c r="Q88">
-        <v>-874.3144337279998</v>
+        <v>-892.6838573759999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2620895779569374</v>
+        <v>0.2787272377997788</v>
       </c>
       <c r="T88">
-        <v>4.995140368520495</v>
+        <v>5.379381935329763</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04612801863118476</v>
+        <v>0.04559781152048149</v>
       </c>
       <c r="W88">
-        <v>0.2249230132067666</v>
+        <v>0.2250480360434705</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1647429236828027</v>
+        <v>0.1628493268588624</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2320263322717906</v>
+        <v>0.2339263322717905</v>
       </c>
       <c r="C89">
-        <v>-7589.374754896588</v>
+        <v>-7712.802453637309</v>
       </c>
       <c r="D89">
-        <v>1507.951245103411</v>
+        <v>1492.721546362691</v>
       </c>
       <c r="E89">
-        <v>5425.025999999999</v>
+        <v>5533.223999999999</v>
       </c>
       <c r="F89">
-        <v>9413.225999999999</v>
+        <v>9521.423999999999</v>
       </c>
       <c r="G89">
         <v>315.9</v>
@@ -8579,37 +8579,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M89">
-        <v>2219.6386908</v>
+        <v>2245.1517792</v>
       </c>
       <c r="N89">
-        <v>-1858.172024133333</v>
+        <v>-1883.685112533333</v>
       </c>
       <c r="O89">
-        <v>-520.2881667573333</v>
+        <v>-527.4318315093334</v>
       </c>
       <c r="P89">
-        <v>-1337.883857376</v>
+        <v>-1356.253281024</v>
       </c>
       <c r="Q89">
-        <v>-892.6838573759999</v>
+        <v>-911.0532810239999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2787272377997788</v>
+        <v>0.2981378409497604</v>
       </c>
       <c r="T89">
-        <v>5.379381935329763</v>
+        <v>5.827663763273911</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04559781152048149</v>
+        <v>0.04507965457138511</v>
       </c>
       <c r="W89">
-        <v>0.2250480360434705</v>
+        <v>0.2251702174520674</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1628493268588624</v>
+        <v>0.1609987663263753</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2339263322717905</v>
+        <v>0.2358263322717906</v>
       </c>
       <c r="C90">
-        <v>-7712.802453637309</v>
+        <v>-7835.925600611323</v>
       </c>
       <c r="D90">
-        <v>1492.721546362691</v>
+        <v>1477.796399388677</v>
       </c>
       <c r="E90">
-        <v>5533.223999999999</v>
+        <v>5641.422</v>
       </c>
       <c r="F90">
-        <v>9521.423999999999</v>
+        <v>9629.621999999999</v>
       </c>
       <c r="G90">
         <v>315.9</v>
@@ -8661,37 +8661,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M90">
-        <v>2245.1517792</v>
+        <v>2270.6648676</v>
       </c>
       <c r="N90">
-        <v>-1883.685112533333</v>
+        <v>-1909.198200933333</v>
       </c>
       <c r="O90">
-        <v>-527.4318315093334</v>
+        <v>-534.5754962613333</v>
       </c>
       <c r="P90">
-        <v>-1356.253281024</v>
+        <v>-1374.622704672</v>
       </c>
       <c r="Q90">
-        <v>-911.0532810239999</v>
+        <v>-929.422704672</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2981378409497604</v>
+        <v>0.3210776446724659</v>
       </c>
       <c r="T90">
-        <v>5.827663763273911</v>
+        <v>6.357451378116994</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04507965457138511</v>
+        <v>0.04457314159867292</v>
       </c>
       <c r="W90">
-        <v>0.2251702174520674</v>
+        <v>0.2252896532110329</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1609987663263753</v>
+        <v>0.1591897914238318</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2358263322717906</v>
+        <v>0.2377263322717905</v>
       </c>
       <c r="C91">
-        <v>-7835.925600611323</v>
+        <v>-7958.753240669585</v>
       </c>
       <c r="D91">
-        <v>1477.796399388677</v>
+        <v>1463.166759330415</v>
       </c>
       <c r="E91">
-        <v>5641.422</v>
+        <v>5749.62</v>
       </c>
       <c r="F91">
-        <v>9629.621999999999</v>
+        <v>9737.82</v>
       </c>
       <c r="G91">
         <v>315.9</v>
@@ -8743,37 +8743,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M91">
-        <v>2270.6648676</v>
+        <v>2296.177956</v>
       </c>
       <c r="N91">
-        <v>-1909.198200933333</v>
+        <v>-1934.711289333333</v>
       </c>
       <c r="O91">
-        <v>-534.5754962613333</v>
+        <v>-541.7191610133334</v>
       </c>
       <c r="P91">
-        <v>-1374.622704672</v>
+        <v>-1392.99212832</v>
       </c>
       <c r="Q91">
-        <v>-929.422704672</v>
+        <v>-947.7921283199998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3210776446724659</v>
+        <v>0.3486054091397124</v>
       </c>
       <c r="T91">
-        <v>6.357451378116994</v>
+        <v>6.993196515928694</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04457314159867292</v>
+        <v>0.04407788446979878</v>
       </c>
       <c r="W91">
-        <v>0.2252896532110329</v>
+        <v>0.2254064348420215</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1591897914238318</v>
+        <v>0.1574210159635671</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2377263322717905</v>
+        <v>0.2396263322717906</v>
       </c>
       <c r="C92">
-        <v>-7958.753240669585</v>
+        <v>-8081.294064011201</v>
       </c>
       <c r="D92">
-        <v>1463.166759330415</v>
+        <v>1448.823935988798</v>
       </c>
       <c r="E92">
-        <v>5749.62</v>
+        <v>5857.818</v>
       </c>
       <c r="F92">
-        <v>9737.82</v>
+        <v>9846.018</v>
       </c>
       <c r="G92">
         <v>315.9</v>
@@ -8825,37 +8825,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M92">
-        <v>2296.177956</v>
+        <v>2321.6910444</v>
       </c>
       <c r="N92">
-        <v>-1934.711289333333</v>
+        <v>-1960.224377733333</v>
       </c>
       <c r="O92">
-        <v>-541.7191610133334</v>
+        <v>-548.8628257653334</v>
       </c>
       <c r="P92">
-        <v>-1392.99212832</v>
+        <v>-1411.361551968</v>
       </c>
       <c r="Q92">
-        <v>-947.7921283199998</v>
+        <v>-966.1615519679999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3486054091397124</v>
+        <v>0.3822504545996805</v>
       </c>
       <c r="T92">
-        <v>6.993196515928694</v>
+        <v>7.770218351031883</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04407788446979878</v>
+        <v>0.0435935121129878</v>
       </c>
       <c r="W92">
-        <v>0.2254064348420215</v>
+        <v>0.2255206498437575</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1574210159635671</v>
+        <v>0.1556911146892421</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2396263322717906</v>
+        <v>0.2415263322717905</v>
       </c>
       <c r="C93">
-        <v>-8081.294064011201</v>
+        <v>-8203.556423397224</v>
       </c>
       <c r="D93">
-        <v>1448.823935988798</v>
+        <v>1434.759576602776</v>
       </c>
       <c r="E93">
-        <v>5857.818</v>
+        <v>5966.016000000001</v>
       </c>
       <c r="F93">
-        <v>9846.018</v>
+        <v>9954.216</v>
       </c>
       <c r="G93">
         <v>315.9</v>
@@ -8907,37 +8907,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M93">
-        <v>2321.6910444</v>
+        <v>2347.2041328</v>
       </c>
       <c r="N93">
-        <v>-1960.224377733333</v>
+        <v>-1985.737466133333</v>
       </c>
       <c r="O93">
-        <v>-548.8628257653334</v>
+        <v>-556.0064905173334</v>
       </c>
       <c r="P93">
-        <v>-1411.361551968</v>
+        <v>-1429.730975616</v>
       </c>
       <c r="Q93">
-        <v>-966.1615519679999</v>
+        <v>-984.5309756159998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3822504545996805</v>
+        <v>0.4243067614246407</v>
       </c>
       <c r="T93">
-        <v>7.770218351031883</v>
+        <v>8.741495644910872</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0435935121129878</v>
+        <v>0.04311966959002055</v>
       </c>
       <c r="W93">
-        <v>0.2255206498437575</v>
+        <v>0.2256323819106732</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1556911146892421</v>
+        <v>0.153998819964359</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2415263322717905</v>
+        <v>0.2434263322717906</v>
       </c>
       <c r="C94">
-        <v>-8203.556423397224</v>
+        <v>-8325.548350371471</v>
       </c>
       <c r="D94">
-        <v>1434.759576602776</v>
+        <v>1420.965649628529</v>
       </c>
       <c r="E94">
-        <v>5966.016000000001</v>
+        <v>6074.214000000001</v>
       </c>
       <c r="F94">
-        <v>9954.216</v>
+        <v>10062.414</v>
       </c>
       <c r="G94">
         <v>315.9</v>
@@ -8989,37 +8989,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M94">
-        <v>2347.2041328</v>
+        <v>2372.7172212</v>
       </c>
       <c r="N94">
-        <v>-1985.737466133333</v>
+        <v>-2011.250554533333</v>
       </c>
       <c r="O94">
-        <v>-556.0064905173334</v>
+        <v>-563.1501552693334</v>
       </c>
       <c r="P94">
-        <v>-1429.730975616</v>
+        <v>-1448.100399264</v>
       </c>
       <c r="Q94">
-        <v>-984.5309756159998</v>
+        <v>-1002.900399264</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4243067614246407</v>
+        <v>0.4783791559138752</v>
       </c>
       <c r="T94">
-        <v>8.741495644910872</v>
+        <v>9.990280737040997</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04311966959002055</v>
+        <v>0.04265601722883752</v>
       </c>
       <c r="W94">
-        <v>0.2256323819106732</v>
+        <v>0.2257417111374401</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.153998819964359</v>
+        <v>0.1523429186744197</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2434263322717906</v>
+        <v>0.2453263322717906</v>
       </c>
       <c r="C95">
-        <v>-8325.548350371471</v>
+        <v>-8447.277570554561</v>
       </c>
       <c r="D95">
-        <v>1420.965649628529</v>
+        <v>1407.434429445438</v>
       </c>
       <c r="E95">
-        <v>6074.214000000001</v>
+        <v>6182.411999999999</v>
       </c>
       <c r="F95">
-        <v>10062.414</v>
+        <v>10170.612</v>
       </c>
       <c r="G95">
         <v>315.9</v>
@@ -9071,37 +9071,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M95">
-        <v>2372.7172212</v>
+        <v>2398.2303096</v>
       </c>
       <c r="N95">
-        <v>-2011.250554533333</v>
+        <v>-2036.763642933333</v>
       </c>
       <c r="O95">
-        <v>-563.1501552693334</v>
+        <v>-570.2938200213334</v>
       </c>
       <c r="P95">
-        <v>-1448.100399264</v>
+        <v>-1466.469822912</v>
       </c>
       <c r="Q95">
-        <v>-1002.900399264</v>
+        <v>-1021.269822912</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4783791559138752</v>
+        <v>0.5504756818995211</v>
       </c>
       <c r="T95">
-        <v>9.990280737040997</v>
+        <v>11.65532752654783</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04265601722883752</v>
+        <v>0.04220222981150947</v>
       </c>
       <c r="W95">
-        <v>0.2257417111374401</v>
+        <v>0.2258487142104461</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1523429186744197</v>
+        <v>0.1507222493268194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2453263322717906</v>
+        <v>0.2472263322717906</v>
       </c>
       <c r="C96">
-        <v>-8447.277570554561</v>
+        <v>-8568.751518072379</v>
       </c>
       <c r="D96">
-        <v>1407.434429445438</v>
+        <v>1394.158481927621</v>
       </c>
       <c r="E96">
-        <v>6182.411999999999</v>
+        <v>6290.61</v>
       </c>
       <c r="F96">
-        <v>10170.612</v>
+        <v>10278.81</v>
       </c>
       <c r="G96">
         <v>315.9</v>
@@ -9153,37 +9153,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M96">
-        <v>2398.2303096</v>
+        <v>2423.743398</v>
       </c>
       <c r="N96">
-        <v>-2036.763642933333</v>
+        <v>-2062.276731333333</v>
       </c>
       <c r="O96">
-        <v>-570.2938200213334</v>
+        <v>-577.4374847733334</v>
       </c>
       <c r="P96">
-        <v>-1466.469822912</v>
+        <v>-1484.83924656</v>
       </c>
       <c r="Q96">
-        <v>-1021.269822912</v>
+        <v>-1039.63924656</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5504756818995211</v>
+        <v>0.6514108182794256</v>
       </c>
       <c r="T96">
-        <v>11.65532752654783</v>
+        <v>13.98639303185741</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04220222981150947</v>
+        <v>0.04175799581349358</v>
       </c>
       <c r="W96">
-        <v>0.2258487142104461</v>
+        <v>0.2259534645871782</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1507222493268194</v>
+        <v>0.1491356993339056</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2472263322717906</v>
+        <v>0.2491263322717905</v>
       </c>
       <c r="C97">
-        <v>-8568.751518072379</v>
+        <v>-8689.97734917554</v>
       </c>
       <c r="D97">
-        <v>1394.158481927621</v>
+        <v>1381.13065082446</v>
       </c>
       <c r="E97">
-        <v>6290.61</v>
+        <v>6398.808</v>
       </c>
       <c r="F97">
-        <v>10278.81</v>
+        <v>10387.008</v>
       </c>
       <c r="G97">
         <v>315.9</v>
@@ -9235,37 +9235,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M97">
-        <v>2423.743398</v>
+        <v>2449.2564864</v>
       </c>
       <c r="N97">
-        <v>-2062.276731333333</v>
+        <v>-2087.789819733333</v>
       </c>
       <c r="O97">
-        <v>-577.4374847733334</v>
+        <v>-584.5811495253334</v>
       </c>
       <c r="P97">
-        <v>-1484.83924656</v>
+        <v>-1503.208670208</v>
       </c>
       <c r="Q97">
-        <v>-1039.63924656</v>
+        <v>-1058.008670208</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6514108182794256</v>
+        <v>0.8028135228492823</v>
       </c>
       <c r="T97">
-        <v>13.98639303185741</v>
+        <v>17.48299128982176</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04175799581349358</v>
+        <v>0.04132301669043635</v>
       </c>
       <c r="W97">
-        <v>0.2259534645871782</v>
+        <v>0.2260560326643951</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1491356993339056</v>
+        <v>0.1475822024658441</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2491263322717905</v>
+        <v>0.2510263322717906</v>
       </c>
       <c r="C98">
-        <v>-8689.97734917554</v>
+        <v>-8810.961955102361</v>
       </c>
       <c r="D98">
-        <v>1381.13065082446</v>
+        <v>1368.344044897638</v>
       </c>
       <c r="E98">
-        <v>6398.808</v>
+        <v>6507.005999999998</v>
       </c>
       <c r="F98">
-        <v>10387.008</v>
+        <v>10495.206</v>
       </c>
       <c r="G98">
         <v>315.9</v>
@@ -9317,37 +9317,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M98">
-        <v>2449.2564864</v>
+        <v>2474.7695748</v>
       </c>
       <c r="N98">
-        <v>-2087.789819733333</v>
+        <v>-2113.302908133333</v>
       </c>
       <c r="O98">
-        <v>-584.5811495253334</v>
+        <v>-591.7248142773333</v>
       </c>
       <c r="P98">
-        <v>-1503.208670208</v>
+        <v>-1521.578093856</v>
       </c>
       <c r="Q98">
-        <v>-1058.008670208</v>
+        <v>-1076.378093856</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8028135228492802</v>
+        <v>1.05515136379904</v>
       </c>
       <c r="T98">
-        <v>17.48299128982172</v>
+        <v>23.31065505309562</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04132301669043635</v>
+        <v>0.04089700620909166</v>
       </c>
       <c r="W98">
-        <v>0.2260560326643951</v>
+        <v>0.2261564859358962</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1475822024658441</v>
+        <v>0.1460607364610416</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2510263322717906</v>
+        <v>0.2529263322717906</v>
       </c>
       <c r="C99">
-        <v>-8810.961955102361</v>
+        <v>-8931.711974233825</v>
       </c>
       <c r="D99">
-        <v>1368.344044897638</v>
+        <v>1355.792025766173</v>
       </c>
       <c r="E99">
-        <v>6507.005999999998</v>
+        <v>6615.203999999999</v>
       </c>
       <c r="F99">
-        <v>10495.206</v>
+        <v>10603.404</v>
       </c>
       <c r="G99">
         <v>315.9</v>
@@ -9399,37 +9399,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M99">
-        <v>2474.7695748</v>
+        <v>2500.2826632</v>
       </c>
       <c r="N99">
-        <v>-2113.302908133333</v>
+        <v>-2138.815996533333</v>
       </c>
       <c r="O99">
-        <v>-591.7248142773333</v>
+        <v>-598.8684790293333</v>
       </c>
       <c r="P99">
-        <v>-1521.578093856</v>
+        <v>-1539.947517504</v>
       </c>
       <c r="Q99">
-        <v>-1076.378093856</v>
+        <v>-1094.747517504</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.05515136379904</v>
+        <v>1.559827045698561</v>
       </c>
       <c r="T99">
-        <v>23.31065505309562</v>
+        <v>34.96598257964344</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04089700620909166</v>
+        <v>0.04047968981920296</v>
       </c>
       <c r="W99">
-        <v>0.2261564859358962</v>
+        <v>0.226254889140632</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1460607364610416</v>
+        <v>0.1445703207828677</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2529263322717906</v>
+        <v>0.2548263322717906</v>
       </c>
       <c r="C100">
-        <v>-8931.711974233825</v>
+        <v>-9052.233803585652</v>
       </c>
       <c r="D100">
-        <v>1355.792025766173</v>
+        <v>1343.468196414346</v>
       </c>
       <c r="E100">
-        <v>6615.203999999999</v>
+        <v>6723.401999999999</v>
       </c>
       <c r="F100">
-        <v>10603.404</v>
+        <v>10711.602</v>
       </c>
       <c r="G100">
         <v>315.9</v>
@@ -9481,37 +9481,37 @@
         <v>361.4666666666668</v>
       </c>
       <c r="M100">
-        <v>2500.2826632</v>
+        <v>2525.7957516</v>
       </c>
       <c r="N100">
-        <v>-2138.815996533333</v>
+        <v>-2164.329084933333</v>
       </c>
       <c r="O100">
-        <v>-598.8684790293333</v>
+        <v>-606.0121437813333</v>
       </c>
       <c r="P100">
-        <v>-1539.947517504</v>
+        <v>-1558.316941152</v>
       </c>
       <c r="Q100">
-        <v>-1094.747517504</v>
+        <v>-1113.116941152</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.559827045698561</v>
+        <v>3.073854091397121</v>
       </c>
       <c r="T100">
-        <v>34.96598257964344</v>
+        <v>69.93196515928686</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04047968981920296</v>
+        <v>0.04007080406345345</v>
       </c>
       <c r="W100">
-        <v>0.226254889140632</v>
+        <v>0.2263513044018377</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1445703207828677</v>
+        <v>0.1431100145123336</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2548263322717906</v>
-      </c>
-      <c r="C101">
-        <v>-9052.233803585652</v>
-      </c>
-      <c r="D101">
-        <v>1343.468196414346</v>
-      </c>
-      <c r="E101">
-        <v>6723.401999999999</v>
-      </c>
-      <c r="F101">
-        <v>10711.602</v>
-      </c>
-      <c r="G101">
-        <v>315.9</v>
-      </c>
-      <c r="H101">
-        <v>6831.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>806.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>445.2</v>
-      </c>
-      <c r="L101">
-        <v>361.4666666666668</v>
-      </c>
-      <c r="M101">
-        <v>2525.7957516</v>
-      </c>
-      <c r="N101">
-        <v>-2164.329084933333</v>
-      </c>
-      <c r="O101">
-        <v>-606.0121437813333</v>
-      </c>
-      <c r="P101">
-        <v>-1558.316941152</v>
-      </c>
-      <c r="Q101">
-        <v>-1113.116941152</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.073854091397121</v>
-      </c>
-      <c r="T101">
-        <v>69.93196515928686</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04007080406345345</v>
-      </c>
-      <c r="W101">
-        <v>0.2263513044018377</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1431100145123336</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
